--- a/saida_skus/SKU_UTD-014-BR-APOIO-COCORAS.xlsx
+++ b/saida_skus/SKU_UTD-014-BR-APOIO-COCORAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 33,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▲ 42,9%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 203,00</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 56,2%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 72,7%</t>
+          <t>R$ 203,00</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 198,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,2%</t>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 373,00</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>▲ 92,3%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,2%</t>
+        <v>60</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 194,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>▲ 385,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,3%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
+          <t>R$ 102,00</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▼ 72,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2,5%</t>
+        <v>28</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,2%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 200,00</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,6%</t>
+          <t>R$ 373,00</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 92,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,9%</t>
+          <t>▼ 13,2%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 255,00</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 43,0%</t>
+          <t>R$ 194,00</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 385,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,2%</t>
+          <t>▼ 7,3%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 447,00</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>▲ 598,4%</t>
+          <t>R$ 40,00</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>▲ 21,6%</t>
+          <t>▲ 2,5%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 64,00</t>
+          <t>R$ 200,00</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>▼ 81,8%</t>
+          <t>▼ 21,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,9%</t>
+          <t>▼ 14,9%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 351,00</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 82,8%</t>
+          <t>R$ 255,00</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 43,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 81,1%</t>
+        <v>47</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
+          <t>R$ 447,00</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 598,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 9,8%</t>
+        <v>62</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21,6%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
+          <t>R$ 64,00</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>▼ 55,4%</t>
+          <t>▼ 81,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 24,2%</t>
+        <v>51</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 287,00</t>
+          <t>R$ 351,00</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>▲ 49,5%</t>
+          <t>▲ 82,8%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 35,3%</t>
+        <v>67</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>▲ 81,1%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1614,22 +1614,22 @@
           <t>R$ 192,00</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▲ 15,9%</t>
+        <v>37</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,8%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
+          <t>R$ 128,00</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>▼ 59,9%</t>
+          <t>▼ 55,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,3%</t>
+        <v>41</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,2%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1757,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 479,00</t>
+          <t>R$ 287,00</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>▲ 15,4%</t>
+          <t>▲ 49,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>33</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 35,3%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 415,00</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>▲ 86,1%</t>
+          <t>R$ 192,00</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>51</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,9%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1903,33 +1903,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 39,4%</t>
+          <t>R$ 192,00</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 59,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>44</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,3%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 160,00</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+          <t>R$ 479,00</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>48</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
+          <t>R$ 415,00</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 86,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>42</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2122,33 +2122,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,6%</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 39,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 36,8%</t>
+        <v>0</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 160,00</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>▼ 30,1%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 65,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 319,00</t>
+          <t>R$ 192,00</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>▲ 121,5%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>▼ 8,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2341,25 +2341,25 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
+          <t>R$ 128,00</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>▼ 46,9%</t>
+          <t>▼ 42,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 4,2%</t>
+        <v>24</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,8%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 271,00</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>▲ 697,1%</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,1%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 65,2%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2487,33 +2487,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 319,00</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 121,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>▼ 30,4%</t>
+          <t>▼ 8,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2560,29 +2560,29 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
+          <t>R$ 144,00</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 46,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,0%</t>
+        <v>25</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▲ 4,2%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2633,33 +2633,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
+          <t>R$ 271,00</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,9%</t>
+          <t>▲ 697,1%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,8%</t>
+        <v>24</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2706,33 +2706,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,6%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>▲ 8,3%</t>
+        <v>16</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,4%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2779,29 +2779,29 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 102,00</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>▼ 41,5%</t>
+          <t>▼ 8,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2852,38 +2852,38 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,9%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▲ 7,9%</t>
+        <v>25</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,8%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2925,25 +2925,25 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>▲ 52,0%</t>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2998,38 +2998,38 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 128,00</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,8%</t>
+          <t>▼ 41,5%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3071,38 +3071,38 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,1%</t>
+          <t>R$ 96,00</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>▲ 7,4%</t>
+          <t>▲ 7,9%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3144,33 +3144,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,9%</t>
+          <t>R$ 96,00</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,6%</t>
+        <v>38</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>▲ 52,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3217,33 +3217,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 6,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>25</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,8%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3290,25 +3290,25 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,1%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>29</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,4%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
@@ -3316,22 +3316,241 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>R$ 192,00</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,9%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,6%</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,2%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
           <t>2,3%</t>
         </is>
       </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>Básica</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O39"/>
+  <autoFilter ref="A1:O42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-014-BR-APOIO-COCORAS.xlsx
+++ b/saida_skus/SKU_UTD-014-BR-APOIO-COCORAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
+          <t>R$ 203,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,0%</t>
+          <t>▲ 49,3%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>▲ 42,9%</t>
+        <v>25</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▼ 56,2%</t>
+          <t>▲ 42,9%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -738,22 +738,22 @@
           <t>R$ 203,00</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 198,5%</t>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 46,7%</t>
+        <v>14</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 56,2%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
@@ -761,7 +761,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 203,00</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 198,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>▼ 72,7%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,2%</t>
+        <v>24</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 373,00</t>
+          <t>R$ 102,00</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>▲ 92,3%</t>
+          <t>▼ 72,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,2%</t>
+        <v>28</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▼ 15,2%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 194,00</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>▲ 385,0%</t>
+          <t>R$ 373,00</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>▲ 92,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,3%</t>
+        <v>33</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>▼ 13,2%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1173,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
+          <t>R$ 194,00</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▲ 385,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>▲ 2,5%</t>
+          <t>▼ 7,3%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
+          <t>13,2%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
           <t>2,4%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 200,00</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,6%</t>
+          <t>R$ 40,00</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,9%</t>
+          <t>▲ 2,5%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 255,00</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 43,0%</t>
+          <t>R$ 200,00</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>▼ 21,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,2%</t>
+        <v>40</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,9%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,14 +1362,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 447,00</t>
+          <t>R$ 255,00</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>▲ 598,4%</t>
+          <t>▼ 43,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>▲ 21,6%</t>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 64,00</t>
+          <t>R$ 447,00</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>▼ 81,8%</t>
+          <t>▲ 598,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,9%</t>
+          <t>▲ 21,6%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,14 +1508,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 351,00</t>
+          <t>R$ 64,00</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>▲ 82,8%</t>
+          <t>▼ 81,8%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>▲ 81,1%</t>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 351,00</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>▲ 82,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▼ 9,8%</t>
+          <t>▲ 81,1%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,14 +1654,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
+          <t>R$ 192,00</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>▼ 55,4%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>▲ 24,2%</t>
+          <t>▼ 9,8%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,14 +1727,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1757,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 287,00</t>
+          <t>R$ 128,00</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>▲ 49,5%</t>
+          <t>▼ 55,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▼ 35,3%</t>
+          <t>▲ 24,2%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,14 +1800,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 287,00</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>▲ 49,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>▲ 15,9%</t>
+          <t>▼ 35,3%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,14 +1873,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1906,22 +1906,22 @@
           <t>R$ 192,00</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 59,9%</t>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>▼ 8,3%</t>
+          <t>▲ 15,9%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,14 +1946,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 479,00</t>
+          <t>R$ 192,00</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>▲ 15,4%</t>
+          <t>▼ 59,9%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▼ 8,3%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,14 +2019,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 415,00</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 86,1%</t>
+          <t>R$ 479,00</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>48</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,14 +2092,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2122,16 +2122,16 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>▲ 39,4%</t>
+          <t>R$ 415,00</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>▲ 86,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2140,15 +2140,15 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,14 +2165,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 160,00</t>
+          <t>R$ 223,00</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▲ 39,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,14 +2238,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2268,20 +2268,20 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
+          <t>R$ 160,00</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2290,11 +2290,11 @@
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,14 +2311,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2341,33 +2341,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
+          <t>R$ 192,00</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>▼ 42,6%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 36,8%</t>
+        <v>0</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,14 +2384,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,1%</t>
+          <t>R$ 128,00</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>▼ 42,6%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>▲ 65,2%</t>
+          <t>▼ 36,8%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,14 +2457,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2487,33 +2487,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 319,00</t>
+          <t>R$ 223,00</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>▲ 121,5%</t>
+          <t>▼ 30,1%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>▼ 8,0%</t>
+          <t>▲ 65,2%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,14 +2530,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2560,33 +2560,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
+          <t>R$ 319,00</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>▼ 46,9%</t>
+          <t>▲ 121,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>▲ 4,2%</t>
+          <t>▼ 8,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,14 +2603,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2633,33 +2633,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 271,00</t>
+          <t>R$ 144,00</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>▲ 697,1%</t>
+          <t>▼ 46,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>25</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▲ 4,2%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,14 +2676,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2706,33 +2706,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 271,00</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 697,1%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>▼ 30,4%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,14 +2749,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2779,38 +2779,38 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,0%</t>
+        <v>16</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▼ 30,4%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -2822,14 +2822,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2852,38 +2852,38 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
+          <t>R$ 102,00</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,9%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,8%</t>
+        <v>23</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▼ 8,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -2895,14 +2895,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2925,33 +2925,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,6%</t>
+          <t>▲ 25,9%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>▲ 8,3%</t>
+          <t>▼ 3,8%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,14 +2968,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2998,38 +2998,38 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
+          <t>R$ 108,00</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>▼ 41,5%</t>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -3041,14 +3041,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3071,33 +3071,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 128,00</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>▲ 7,9%</t>
+          <t>▼ 41,5%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3114,14 +3114,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3149,20 +3149,20 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>▲ 52,0%</t>
+        <v>41</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▲ 7,9%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -3187,14 +3187,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3217,33 +3217,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 96,00</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,8%</t>
+          <t>▲ 52,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,14 +3260,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3290,33 +3290,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>▲ 7,4%</t>
+          <t>▼ 13,8%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,14 +3333,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3363,33 +3363,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
+          <t>R$ 223,00</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,9%</t>
+          <t>▲ 16,1%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>▼ 3,6%</t>
+          <t>▲ 7,4%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3406,14 +3406,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3436,33 +3436,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 192,00</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>▲ 6,2%</t>
+          <t>▼ 13,9%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 3,6%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,14 +3479,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3509,25 +3509,25 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▲ 6,2%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>28</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
@@ -3535,22 +3535,95 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
           <t>2,3%</t>
         </is>
       </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>Básica</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O42"/>
+  <autoFilter ref="A1:O43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-014-BR-APOIO-COCORAS.xlsx
+++ b/saida_skus/SKU_UTD-014-BR-APOIO-COCORAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -594,20 +594,20 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▲ 49,3%</t>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
+          <t>R$ 271,00</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,0%</t>
+          <t>▲ 99,3%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▲ 42,9%</t>
+        <v>32</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>▲ 23,1%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>▼ 56,2%</t>
+          <t>▲ 4,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -811,22 +811,22 @@
           <t>R$ 203,00</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>▲ 198,5%</t>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 49,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>▼ 46,7%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
@@ -834,7 +834,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>20</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 42,9%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 203,00</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>14</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 56,2%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
+          <t>R$ 203,00</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>▼ 72,7%</t>
+          <t>▲ 198,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▼ 15,2%</t>
+        <v>32</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 373,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>▲ 92,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>▼ 13,2%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 194,00</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>▲ 385,0%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▼ 7,3%</t>
+        <v>24</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+          <t>R$ 102,00</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 72,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>▲ 2,5%</t>
+          <t>▼ 15,2%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 200,00</t>
+          <t>R$ 373,00</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>▼ 21,6%</t>
+          <t>▲ 92,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▼ 14,9%</t>
+        <v>33</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,2%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 255,00</t>
+          <t>R$ 194,00</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>▼ 43,0%</t>
+          <t>▲ 385,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▼ 24,2%</t>
+        <v>38</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,3%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 447,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>▲ 598,4%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▲ 21,6%</t>
+        <v>41</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2,5%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 64,00</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>▼ 81,8%</t>
+          <t>R$ 200,00</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,6%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>▼ 23,9%</t>
+        <v>40</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,9%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 351,00</t>
+          <t>R$ 255,00</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>▲ 82,8%</t>
+          <t>▼ 43,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▲ 81,1%</t>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 447,00</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>▲ 598,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>▼ 9,8%</t>
+          <t>▲ 21,6%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1757,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>▼ 55,4%</t>
+          <t>R$ 64,00</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 81,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▲ 24,2%</t>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 287,00</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>▲ 49,5%</t>
+          <t>R$ 351,00</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>▲ 82,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>▼ 35,3%</t>
+          <t>▲ 81,1%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1906,22 +1906,22 @@
           <t>R$ 192,00</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>▲ 15,9%</t>
+          <t>▼ 9,8%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>▼ 59,9%</t>
+          <t>R$ 128,00</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 55,4%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>▼ 8,3%</t>
+          <t>▲ 24,2%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 479,00</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>▲ 15,4%</t>
+          <t>R$ 287,00</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 49,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▼ 35,3%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2122,33 +2122,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 415,00</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>▲ 86,1%</t>
+          <t>R$ 192,00</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>51</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,9%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 192,00</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>▲ 39,4%</t>
+          <t>▼ 59,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>44</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,3%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 160,00</t>
+          <t>R$ 479,00</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>48</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2341,33 +2341,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 415,00</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 86,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>42</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
+          <t>R$ 223,00</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>▼ 42,6%</t>
+          <t>▲ 39,4%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▼ 36,8%</t>
+        <v>0</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2487,33 +2487,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>▼ 30,1%</t>
+          <t>R$ 160,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▲ 65,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2560,33 +2560,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 319,00</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>▲ 121,5%</t>
+          <t>R$ 192,00</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▼ 8,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2633,25 +2633,25 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 46,9%</t>
+          <t>R$ 128,00</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>▲ 4,2%</t>
+          <t>▼ 36,8%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2706,33 +2706,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 271,00</t>
+          <t>R$ 223,00</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>▲ 697,1%</t>
+          <t>▼ 30,1%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>38</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▲ 65,2%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2779,33 +2779,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 319,00</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 121,5%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▼ 30,4%</t>
+        <v>23</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2852,29 +2852,29 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,9%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>▼ 8,0%</t>
+          <t>▲ 4,2%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2925,33 +2925,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▲ 25,9%</t>
+          <t>R$ 271,00</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 697,1%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>▼ 3,8%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>▼ 15,6%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>▲ 8,3%</t>
+          <t>▼ 30,4%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3071,29 +3071,29 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
+          <t>R$ 102,00</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▼ 41,5%</t>
+        <v>23</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
@@ -3114,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3144,38 +3144,38 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,9%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>▲ 7,9%</t>
+          <t>▼ 3,8%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3217,25 +3217,25 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▲ 52,0%</t>
+        <v>26</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3290,38 +3290,38 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 128,00</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>▼ 13,8%</t>
+        <v>24</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 41,5%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3363,38 +3363,38 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▲ 16,1%</t>
+          <t>R$ 96,00</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▲ 7,4%</t>
+        <v>41</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,9%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3436,33 +3436,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>▼ 13,9%</t>
+          <t>R$ 96,00</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>▼ 3,6%</t>
+          <t>▲ 52,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3509,33 +3509,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>▲ 6,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 13,8%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3582,25 +3582,25 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,1%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>29</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,4%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
@@ -3608,22 +3608,241 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>R$ 192,00</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,9%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,6%</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,2%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
           <t>2,3%</t>
         </is>
       </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>Básica</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O43"/>
+  <autoFilter ref="A1:O46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-014-BR-APOIO-COCORAS.xlsx
+++ b/saida_skus/SKU_UTD-014-BR-APOIO-COCORAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
+          <t>R$ 200,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,1%</t>
+          <t>▼ 26,2%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>41</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -667,20 +667,20 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>▲ 99,3%</t>
+          <t>▲ 33,5%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>▲ 23,1%</t>
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
@@ -688,7 +688,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,0%</t>
+          <t>R$ 203,00</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>▲ 4,0%</t>
+          <t>▲ 81,2%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -811,22 +811,22 @@
           <t>R$ 203,00</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>▲ 49,3%</t>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>16</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,0%</t>
+          <t>R$ 271,00</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>▲ 42,9%</t>
+          <t>▲ 23,1%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 56,2%</t>
+        <v>26</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>▲ 4,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1032,20 +1032,20 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>▲ 198,5%</t>
+          <t>▲ 49,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 46,7%</t>
+        <v>25</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 33,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▲ 42,9%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 203,00</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 56,2%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 72,7%</t>
+          <t>R$ 203,00</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>▲ 198,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,2%</t>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 373,00</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 92,3%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,2%</t>
+        <v>60</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 194,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>▲ 385,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,3%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
+          <t>R$ 102,00</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▼ 72,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2,5%</t>
+        <v>28</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,2%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 200,00</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,6%</t>
+          <t>R$ 373,00</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>▲ 92,3%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,9%</t>
+          <t>▼ 13,2%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 255,00</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 43,0%</t>
+          <t>R$ 194,00</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 385,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,2%</t>
+          <t>▼ 7,3%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 447,00</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>▲ 598,4%</t>
+          <t>R$ 40,00</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>▲ 21,6%</t>
+          <t>▲ 2,5%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1757,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 64,00</t>
+          <t>R$ 200,00</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>▼ 81,8%</t>
+          <t>▼ 21,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,9%</t>
+          <t>▼ 14,9%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 351,00</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>▲ 82,8%</t>
+          <t>R$ 255,00</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 43,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>▲ 81,1%</t>
+        <v>47</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1903,33 +1903,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
+          <t>R$ 447,00</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 598,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 9,8%</t>
+        <v>62</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21,6%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
+          <t>R$ 64,00</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>▼ 55,4%</t>
+          <t>▼ 81,8%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▲ 24,2%</t>
+        <v>51</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 287,00</t>
+          <t>R$ 351,00</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>▲ 49,5%</t>
+          <t>▲ 82,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 35,3%</t>
+        <v>67</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 81,1%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2125,22 +2125,22 @@
           <t>R$ 192,00</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>▲ 15,9%</t>
+        <v>37</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,8%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
+          <t>R$ 128,00</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>▼ 59,9%</t>
+          <t>▼ 55,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,3%</t>
+        <v>41</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,2%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 479,00</t>
+          <t>R$ 287,00</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>▲ 15,4%</t>
+          <t>▲ 49,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>33</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 35,3%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2341,33 +2341,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 415,00</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 86,1%</t>
+          <t>R$ 192,00</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>51</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,9%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>▲ 39,4%</t>
+          <t>R$ 192,00</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 59,9%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>44</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,3%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2487,33 +2487,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 160,00</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+          <t>R$ 479,00</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>48</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2560,33 +2560,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
+          <t>R$ 415,00</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 86,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>42</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2633,33 +2633,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,6%</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 39,4%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 36,8%</t>
+        <v>0</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2706,33 +2706,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 160,00</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>▼ 30,1%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>▲ 65,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2779,33 +2779,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 319,00</t>
+          <t>R$ 192,00</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>▲ 121,5%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>▼ 8,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2852,25 +2852,25 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
+          <t>R$ 128,00</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>▼ 46,9%</t>
+          <t>▼ 42,6%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▲ 4,2%</t>
+        <v>24</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,8%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2925,33 +2925,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 271,00</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 697,1%</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,1%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 65,2%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 319,00</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>▲ 121,5%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>▼ 30,4%</t>
+          <t>▼ 8,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3071,29 +3071,29 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
+          <t>R$ 144,00</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 46,9%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,0%</t>
+        <v>25</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 4,2%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3144,33 +3144,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
+          <t>R$ 271,00</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,9%</t>
+          <t>▲ 697,1%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,8%</t>
+        <v>24</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3217,33 +3217,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,6%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 8,3%</t>
+        <v>16</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,4%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3290,29 +3290,29 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 102,00</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>▼ 41,5%</t>
+          <t>▼ 8,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
@@ -3333,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3363,38 +3363,38 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,9%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▲ 7,9%</t>
+        <v>25</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,8%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3436,25 +3436,25 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>▲ 52,0%</t>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3509,38 +3509,38 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 128,00</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,8%</t>
+          <t>▼ 41,5%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3582,38 +3582,38 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,1%</t>
+          <t>R$ 96,00</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>▲ 7,4%</t>
+          <t>▲ 7,9%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3655,33 +3655,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,9%</t>
+          <t>R$ 96,00</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,6%</t>
+        <v>38</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 52,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3728,33 +3728,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>▲ 6,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>25</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,8%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3801,25 +3801,25 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,1%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>29</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,4%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
@@ -3827,22 +3827,241 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>R$ 192,00</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,9%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,6%</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,2%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
           <t>2,3%</t>
         </is>
       </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>Básica</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O46"/>
+  <autoFilter ref="A1:O49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-014-BR-APOIO-COCORAS.xlsx
+++ b/saida_skus/SKU_UTD-014-BR-APOIO-COCORAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -589,12 +589,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 200,00</t>
+          <t>R$ 259,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▼ 26,2%</t>
+          <t>▲ 29,5%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
@@ -602,20 +602,20 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 271,00</t>
+          <t>R$ 200,00</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,5%</t>
+          <t>▼ 26,2%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>41</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 271,00</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>▲ 81,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -811,30 +811,30 @@
           <t>R$ 203,00</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,1%</t>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 81,2%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 271,00</t>
+          <t>R$ 203,00</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>▲ 99,3%</t>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>▲ 23,1%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
+          <t>R$ 271,00</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,0%</t>
+          <t>▲ 99,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>▲ 4,0%</t>
+        <v>32</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▲ 23,1%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>▲ 49,3%</t>
+          <t>▼ 33,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>26</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▲ 4,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
+          <t>R$ 203,00</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,0%</t>
+          <t>▲ 49,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>▲ 42,9%</t>
+        <v>25</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1173,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 56,2%</t>
+          <t>▲ 42,9%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1249,22 +1249,22 @@
           <t>R$ 203,00</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>▲ 198,5%</t>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 46,7%</t>
+        <v>14</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>▼ 56,2%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 203,00</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 198,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,14 +1362,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>▼ 72,7%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,2%</t>
+        <v>24</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,14 +1508,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 373,00</t>
+          <t>R$ 102,00</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>▲ 92,3%</t>
+          <t>▼ 72,7%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,2%</t>
+        <v>28</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>▼ 15,2%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 194,00</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>▲ 385,0%</t>
+          <t>R$ 373,00</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>▲ 92,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,3%</t>
+        <v>33</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▼ 13,2%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,14 +1654,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
+          <t>R$ 194,00</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▲ 385,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>▲ 2,5%</t>
+          <t>▼ 7,3%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
+          <t>13,2%</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
           <t>2,4%</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,14 +1727,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1757,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 200,00</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,6%</t>
+          <t>R$ 40,00</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,9%</t>
+          <t>▲ 2,5%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,14 +1800,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 255,00</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 43,0%</t>
+          <t>R$ 200,00</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>▼ 21,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,2%</t>
+        <v>40</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,9%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,14 +1873,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1903,33 +1903,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 447,00</t>
+          <t>R$ 255,00</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>▲ 598,4%</t>
+          <t>▼ 43,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>▲ 21,6%</t>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,14 +1946,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 64,00</t>
+          <t>R$ 447,00</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>▼ 81,8%</t>
+          <t>▲ 598,4%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,9%</t>
+          <t>▲ 21,6%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,14 +2019,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 351,00</t>
+          <t>R$ 64,00</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>▲ 82,8%</t>
+          <t>▼ 81,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>▲ 81,1%</t>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,14 +2092,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2122,33 +2122,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 351,00</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>▲ 82,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>▼ 9,8%</t>
+          <t>▲ 81,1%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,14 +2165,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
+          <t>R$ 192,00</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>▼ 55,4%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>▲ 24,2%</t>
+          <t>▼ 9,8%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,14 +2238,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 287,00</t>
+          <t>R$ 128,00</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>▲ 49,5%</t>
+          <t>▼ 55,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>▼ 35,3%</t>
+          <t>▲ 24,2%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,14 +2311,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2341,33 +2341,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 287,00</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>▲ 49,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>▲ 15,9%</t>
+          <t>▼ 35,3%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,14 +2384,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2417,22 +2417,22 @@
           <t>R$ 192,00</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 59,9%</t>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>▼ 8,3%</t>
+          <t>▲ 15,9%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,14 +2457,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2487,33 +2487,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 479,00</t>
+          <t>R$ 192,00</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>▲ 15,4%</t>
+          <t>▼ 59,9%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▼ 8,3%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,14 +2530,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2560,33 +2560,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 415,00</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>▲ 86,1%</t>
+          <t>R$ 479,00</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>48</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,14 +2603,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2633,16 +2633,16 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 39,4%</t>
+          <t>R$ 415,00</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>▲ 86,1%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2651,15 +2651,15 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,14 +2676,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2706,12 +2706,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 160,00</t>
+          <t>R$ 223,00</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▲ 39,4%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,14 +2749,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2779,20 +2779,20 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
+          <t>R$ 160,00</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2801,11 +2801,11 @@
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,14 +2822,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2852,33 +2852,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
+          <t>R$ 192,00</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>▼ 42,6%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 36,8%</t>
+        <v>0</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,14 +2895,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2925,33 +2925,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,1%</t>
+          <t>R$ 128,00</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>▼ 42,6%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>▲ 65,2%</t>
+          <t>▼ 36,8%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,14 +2968,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 319,00</t>
+          <t>R$ 223,00</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>▲ 121,5%</t>
+          <t>▼ 30,1%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>▼ 8,0%</t>
+          <t>▲ 65,2%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,14 +3041,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3071,33 +3071,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
+          <t>R$ 319,00</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>▼ 46,9%</t>
+          <t>▲ 121,5%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>▲ 4,2%</t>
+          <t>▼ 8,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3114,14 +3114,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3144,33 +3144,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 271,00</t>
+          <t>R$ 144,00</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>▲ 697,1%</t>
+          <t>▼ 46,9%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>25</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▲ 4,2%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,14 +3187,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3217,33 +3217,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 271,00</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 697,1%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>▼ 30,4%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,14 +3260,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3290,38 +3290,38 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,0%</t>
+        <v>16</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▼ 30,4%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -3333,14 +3333,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3363,38 +3363,38 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
+          <t>R$ 102,00</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,9%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,8%</t>
+        <v>23</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▼ 8,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -3406,14 +3406,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3436,33 +3436,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,6%</t>
+          <t>▲ 25,9%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>▲ 8,3%</t>
+          <t>▼ 3,8%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,14 +3479,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3509,38 +3509,38 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
+          <t>R$ 108,00</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>▼ 41,5%</t>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -3552,14 +3552,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3582,33 +3582,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 128,00</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>▲ 7,9%</t>
+          <t>▼ 41,5%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,14 +3625,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3660,20 +3660,20 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▲ 52,0%</t>
+        <v>41</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▲ 7,9%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
@@ -3681,12 +3681,12 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -3698,14 +3698,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3728,33 +3728,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 96,00</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,8%</t>
+          <t>▲ 52,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,14 +3771,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3801,33 +3801,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>▲ 7,4%</t>
+          <t>▼ 13,8%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3844,14 +3844,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3874,33 +3874,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
+          <t>R$ 223,00</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,9%</t>
+          <t>▲ 16,1%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>▼ 3,6%</t>
+          <t>▲ 7,4%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,14 +3917,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3947,33 +3947,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 192,00</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>▲ 6,2%</t>
+          <t>▼ 13,9%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 3,6%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3990,14 +3990,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4020,25 +4020,25 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>▲ 6,2%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>28</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
@@ -4046,22 +4046,95 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
           <t>2,3%</t>
         </is>
       </c>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>Básica</t>
-        </is>
-      </c>
-      <c r="O49" s="2" t="inlineStr">
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O49"/>
+  <autoFilter ref="A1:O50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-014-BR-APOIO-COCORAS.xlsx
+++ b/saida_skus/SKU_UTD-014-BR-APOIO-COCORAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O50"/>
+  <dimension ref="A1:O52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,25 +589,25 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 259,00</t>
+          <t>R$ 251,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▲ 29,5%</t>
+          <t>▲ 74,3%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>29</v>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>▼ 3,3%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,25 +662,25 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 200,00</t>
+          <t>R$ 144,00</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>▼ 26,2%</t>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>30</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>▼ 26,8%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
@@ -688,7 +688,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 271,00</t>
+          <t>R$ 259,00</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,5%</t>
+          <t>▲ 29,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>41</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 200,00</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>▼ 26,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▲ 81,2%</t>
+        <v>41</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,1%</t>
+          <t>R$ 271,00</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 271,00</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>▲ 99,3%</t>
+          <t>R$ 203,00</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>▲ 23,1%</t>
+          <t>▲ 81,2%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
+          <t>R$ 203,00</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,0%</t>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▲ 4,0%</t>
+        <v>16</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
+          <t>R$ 271,00</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>▲ 49,3%</t>
+          <t>▲ 99,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 23,1%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▲ 42,9%</t>
+          <t>▲ 4,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1249,22 +1249,22 @@
           <t>R$ 203,00</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>▲ 49,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>▼ 56,2%</t>
+        <v>25</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>▲ 198,5%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▼ 46,7%</t>
+        <v>20</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▲ 42,9%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 203,00</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▼ 56,2%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
+          <t>R$ 203,00</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 198,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>▼ 72,7%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>▼ 15,2%</t>
+        <v>60</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 373,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>▲ 92,3%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>▼ 13,2%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 194,00</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>▲ 385,0%</t>
+          <t>R$ 102,00</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>▼ 72,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>▼ 7,3%</t>
+          <t>▼ 15,2%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1757,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+          <t>R$ 373,00</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▲ 92,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▲ 2,5%</t>
+        <v>33</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▼ 13,2%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1830,25 +1830,25 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 200,00</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>▼ 21,6%</t>
+          <t>R$ 194,00</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>▲ 385,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>▼ 14,9%</t>
+          <t>▼ 7,3%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1903,33 +1903,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 255,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>▼ 43,0%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▼ 24,2%</t>
+        <v>41</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▲ 2,5%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 447,00</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>▲ 598,4%</t>
+          <t>R$ 200,00</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>▼ 21,6%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▲ 21,6%</t>
+        <v>40</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,9%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 64,00</t>
+          <t>R$ 255,00</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>▼ 81,8%</t>
+          <t>▼ 43,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>▼ 23,9%</t>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2122,33 +2122,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 351,00</t>
+          <t>R$ 447,00</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>▲ 82,8%</t>
+          <t>▲ 598,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>▲ 81,1%</t>
+          <t>▲ 21,6%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 64,00</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>▼ 81,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>▼ 9,8%</t>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>▼ 55,4%</t>
+          <t>R$ 351,00</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>▲ 82,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>▲ 24,2%</t>
+          <t>▲ 81,1%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2341,33 +2341,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 287,00</t>
+          <t>R$ 192,00</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>▲ 49,5%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>▼ 35,3%</t>
+          <t>▼ 9,8%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 128,00</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>▼ 55,4%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>▲ 15,9%</t>
+          <t>▲ 24,2%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2487,29 +2487,29 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>▼ 59,9%</t>
+          <t>R$ 287,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▲ 49,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>▼ 8,3%</t>
+          <t>▼ 35,3%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2560,33 +2560,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 479,00</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>▲ 15,4%</t>
+          <t>R$ 192,00</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▲ 15,9%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2633,33 +2633,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 415,00</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>▲ 86,1%</t>
+          <t>R$ 192,00</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>▼ 59,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>44</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▼ 8,3%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2706,33 +2706,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 479,00</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>▲ 39,4%</t>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>48</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2779,16 +2779,16 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 160,00</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+          <t>R$ 415,00</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>▲ 86,1%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2797,15 +2797,15 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2852,20 +2852,20 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
+          <t>R$ 223,00</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 39,4%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2874,11 +2874,11 @@
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2925,33 +2925,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
+          <t>R$ 160,00</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>▼ 42,6%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▼ 36,8%</t>
+        <v>0</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>▼ 30,1%</t>
+          <t>R$ 192,00</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▲ 65,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3071,33 +3071,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 319,00</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>▲ 121,5%</t>
+          <t>R$ 128,00</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>▼ 42,6%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>▼ 8,0%</t>
+          <t>▼ 36,8%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3144,33 +3144,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
+          <t>R$ 223,00</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>▼ 46,9%</t>
+          <t>▼ 30,1%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>▲ 4,2%</t>
+          <t>▲ 65,2%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3217,33 +3217,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 271,00</t>
+          <t>R$ 319,00</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>▲ 697,1%</t>
+          <t>▲ 121,5%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>23</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▼ 8,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3290,33 +3290,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 144,00</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 46,9%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>▼ 30,4%</t>
+        <v>25</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▲ 4,2%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3363,38 +3363,38 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+          <t>R$ 271,00</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▲ 697,1%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▼ 8,0%</t>
+        <v>24</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3436,33 +3436,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>▲ 25,9%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>▼ 3,8%</t>
+          <t>▼ 30,4%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3509,25 +3509,25 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
+          <t>R$ 102,00</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>▼ 15,6%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▲ 8,3%</t>
+        <v>23</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▼ 8,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
@@ -3535,12 +3535,12 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3582,25 +3582,25 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 25,9%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>▼ 41,5%</t>
+          <t>▼ 3,8%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3655,25 +3655,25 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>▲ 7,9%</t>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
@@ -3681,12 +3681,12 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3728,38 +3728,38 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 128,00</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▲ 52,0%</t>
+        <v>24</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▼ 41,5%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3801,38 +3801,38 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 96,00</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 13,8%</t>
+        <v>41</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▲ 7,9%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3874,33 +3874,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>▲ 16,1%</t>
+          <t>R$ 96,00</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>▲ 7,4%</t>
+          <t>▲ 52,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3947,33 +3947,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>▼ 13,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>▼ 3,6%</t>
+          <t>▼ 13,8%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4025,20 +4025,20 @@
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>▲ 6,2%</t>
+          <t>▲ 16,1%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 7,4%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4063,78 +4063,224 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>R$ 192,00</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>▼ 13,9%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▼ 3,6%</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>▲ 6,2%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>UTD-014-BR</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Apoio cocoras</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>5333038712</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>R$ 39,90</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>R$ 210,00</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="n">
+      <c r="I52" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="J52" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
+      <c r="K52" s="2" t="inlineStr">
         <is>
           <t>33,3%</t>
         </is>
       </c>
-      <c r="L50" s="2" t="n">
+      <c r="L52" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="M50" s="2" t="inlineStr">
+      <c r="M52" s="2" t="inlineStr">
         <is>
           <t>2,3%</t>
         </is>
       </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>Básica</t>
-        </is>
-      </c>
-      <c r="O50" s="2" t="inlineStr">
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O50"/>
+  <autoFilter ref="A1:O52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-014-BR-APOIO-COCORAS.xlsx
+++ b/saida_skus/SKU_UTD-014-BR-APOIO-COCORAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O52"/>
+  <dimension ref="A1:O64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 251,00</t>
+          <t>R$ 291,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▲ 74,3%</t>
+          <t>▼ 26,3%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>▼ 3,3%</t>
+        <v>31</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 22,5%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -625,19 +625,19 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
+          <t>R$ 395,00</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>▼ 44,4%</t>
+          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>▼ 26,8%</t>
+        <v>40</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 259,00</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>▲ 29,5%</t>
+          <t>R$ 359,00</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>56</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 30,2%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 200,00</t>
+          <t>R$ 287,00</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>▼ 26,2%</t>
+          <t>▲ 99,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>43</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,5%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 271,00</t>
+          <t>R$ 144,00</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,5%</t>
+          <t>▼ 42,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 37,9%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 251,00</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>▲ 74,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
@@ -967,20 +967,20 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>▲ 81,2%</t>
+          <t>▼ 17,1%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,1%</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 9,4%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 271,00</t>
+          <t>R$ 287,00</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>▲ 99,3%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>▲ 23,1%</t>
+          <t>▼ 31,9%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
+          <t>R$ 503,00</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,0%</t>
+          <t>▲ 179,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▲ 4,0%</t>
+        <v>47</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 27,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
+          <t>R$ 180,00</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>▲ 49,3%</t>
+          <t>▼ 16,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>37</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,0%</t>
+          <t>R$ 215,00</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▲ 42,9%</t>
+        <v>27</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 17,4%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 287,00</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▼ 56,2%</t>
+        <v>23</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,7%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>▲ 198,5%</t>
+          <t>R$ 251,00</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 74,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▼ 46,7%</t>
+        <v>29</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,3%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▼ 26,8%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 259,00</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 29,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>41</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>▼ 72,7%</t>
+          <t>R$ 200,00</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 26,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▼ 15,2%</t>
+        <v>41</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1757,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 373,00</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>▲ 92,3%</t>
+          <t>R$ 271,00</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▼ 13,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1830,25 +1830,25 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 194,00</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>▲ 385,0%</t>
+          <t>R$ 203,00</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>▼ 7,3%</t>
+          <t>▲ 81,2%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1903,33 +1903,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+          <t>R$ 203,00</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>▲ 2,5%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 200,00</t>
+          <t>R$ 271,00</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>▼ 21,6%</t>
+          <t>▲ 99,3%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>▼ 14,9%</t>
+          <t>▲ 23,1%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 255,00</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>▼ 43,0%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>▼ 24,2%</t>
+          <t>▲ 4,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2122,33 +2122,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 447,00</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>▲ 598,4%</t>
+          <t>R$ 203,00</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 49,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▲ 21,6%</t>
+        <v>25</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 64,00</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>▼ 81,8%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>▼ 23,9%</t>
+          <t>▲ 42,9%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 351,00</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>▲ 82,8%</t>
+          <t>R$ 203,00</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>▲ 81,1%</t>
+          <t>▼ 56,2%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2341,25 +2341,25 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 203,00</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 198,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▼ 9,8%</t>
+        <v>32</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>▼ 55,4%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▲ 24,2%</t>
+        <v>60</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2487,33 +2487,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 287,00</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▲ 49,5%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▼ 35,3%</t>
+        <v>24</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2560,33 +2560,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 102,00</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 72,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>▲ 15,9%</t>
+          <t>▼ 15,2%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2633,33 +2633,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
+          <t>R$ 373,00</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>▼ 59,9%</t>
+          <t>▲ 92,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 8,3%</t>
+        <v>33</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,2%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2706,33 +2706,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 479,00</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>▲ 15,4%</t>
+          <t>R$ 194,00</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>▲ 385,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▼ 7,3%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2779,33 +2779,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 415,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>▲ 86,1%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>41</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2,5%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2852,25 +2852,25 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 200,00</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>▲ 39,4%</t>
+          <t>▼ 21,6%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>40</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,9%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2925,33 +2925,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 160,00</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+          <t>R$ 255,00</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 43,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>47</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 447,00</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>▲ 598,4%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 21,6%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3071,33 +3071,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>▼ 42,6%</t>
+          <t>R$ 64,00</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 81,8%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▼ 36,8%</t>
+        <v>51</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3144,33 +3144,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 351,00</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>▼ 30,1%</t>
+          <t>▲ 82,8%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▲ 65,2%</t>
+        <v>67</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>▲ 81,1%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3217,29 +3217,29 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 319,00</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>▲ 121,5%</t>
+          <t>R$ 192,00</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▼ 8,0%</t>
+        <v>37</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,8%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3290,25 +3290,25 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>▼ 46,9%</t>
+          <t>R$ 128,00</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 55,4%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▲ 4,2%</t>
+        <v>41</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,2%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3363,33 +3363,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 271,00</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▲ 697,1%</t>
+          <t>R$ 287,00</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 49,5%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 35,3%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3436,33 +3436,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 192,00</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>▼ 30,4%</t>
+          <t>▲ 15,9%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3509,38 +3509,38 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+          <t>R$ 192,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 59,9%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▼ 8,0%</t>
+        <v>44</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,3%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3582,33 +3582,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>▲ 25,9%</t>
+          <t>R$ 479,00</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>▼ 3,8%</t>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3655,33 +3655,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
+          <t>R$ 415,00</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>▼ 15,6%</t>
+          <t>▲ 86,1%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▲ 8,3%</t>
+        <v>42</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3728,38 +3728,38 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>▲ 39,4%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>▼ 41,5%</t>
+        <v>0</v>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3801,38 +3801,38 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 160,00</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▲ 7,9%</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3874,33 +3874,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 192,00</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>▲ 52,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3947,33 +3947,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 128,00</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,6%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▼ 13,8%</t>
+        <v>24</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,8%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4025,20 +4025,20 @@
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>▲ 16,1%</t>
+          <t>▼ 30,1%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▲ 7,4%</t>
+        <v>38</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>▲ 65,2%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4093,33 +4093,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
+          <t>R$ 319,00</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>▼ 13,9%</t>
+          <t>▲ 121,5%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▼ 3,6%</t>
+        <v>23</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4166,33 +4166,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 144,00</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>▲ 6,2%</t>
+          <t>▼ 46,9%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>25</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>▲ 4,2%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4209,78 +4209,954 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>R$ 271,00</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>▲ 697,1%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,4%</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>6,3%</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>R$ 102,00</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,0%</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>13,0%</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,9%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,8%</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>16,0%</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,6%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,3%</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>11,5%</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>R$ 128,00</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 41,5%</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>R$ 96,00</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,9%</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>7,3%</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>R$ 96,00</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>▲ 52,0%</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>7,9%</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,8%</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,1%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,4%</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>24,1%</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>R$ 192,00</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,9%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,6%</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,2%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>UTD-014-BR</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Apoio cocoras</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>5333038712</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>R$ 39,90</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>R$ 210,00</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="2" t="n">
+      <c r="I64" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="J64" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr">
+      <c r="K64" s="2" t="inlineStr">
         <is>
           <t>33,3%</t>
         </is>
       </c>
-      <c r="L52" s="2" t="n">
+      <c r="L64" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="M52" s="2" t="inlineStr">
+      <c r="M64" s="2" t="inlineStr">
         <is>
           <t>2,3%</t>
         </is>
       </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>Básica</t>
-        </is>
-      </c>
-      <c r="O52" s="2" t="inlineStr">
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O52"/>
+  <autoFilter ref="A1:O64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-014-BR-APOIO-COCORAS.xlsx
+++ b/saida_skus/SKU_UTD-014-BR-APOIO-COCORAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O64"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,12 +589,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 291,00</t>
+          <t>R$ 108,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▼ 26,3%</t>
+          <t>▼ 66,6%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
@@ -602,20 +602,20 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 22,5%</t>
+          <t>▼ 6,1%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,29 +662,29 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
+          <t>R$ 323,00</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>▲ 10,0%</t>
+          <t>▲ 50,2%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+        <v>33</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>▲ 43,5%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
@@ -698,19 +698,19 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 359,00</t>
+          <t>R$ 215,00</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,1%</t>
+          <t>▲ 198,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 30,2%</t>
+        <v>23</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,1%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -771,19 +771,19 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 287,00</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>▲ 99,3%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>▲ 7,5%</t>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -844,19 +844,19 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,6%</t>
+          <t>R$ 215,00</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 19,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 37,9%</t>
+        <v>28</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -917,19 +917,19 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 251,00</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>▲ 74,3%</t>
+          <t>R$ 180,00</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 32,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 17,1%</t>
+        <v>28</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,7%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -990,19 +990,19 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,8%</t>
+          <t>R$ 267,00</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 9,4%</t>
+        <v>27</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 38,6%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1063,19 +1063,19 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 287,00</t>
+          <t>R$ 160,00</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>▼ 42,9%</t>
+          <t>▼ 55,4%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 31,9%</t>
+        <v>44</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1136,19 +1136,19 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 503,00</t>
+          <t>R$ 359,00</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>▲ 179,4%</t>
+          <t>▲ 50,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▲ 27,0%</t>
+        <v>44</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,2%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1209,19 +1209,19 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 180,00</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,3%</t>
+          <t>R$ 239,00</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>▲ 37,0%</t>
+          <t>▲ 45,2%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1282,19 +1282,19 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 215,00</t>
+          <t>R$ 120,00</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,1%</t>
+          <t>▼ 57,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 17,4%</t>
+        <v>31</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1355,19 +1355,19 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 287,00</t>
+          <t>R$ 279,00</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▲ 39,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1428,19 +1428,19 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 251,00</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 74,3%</t>
+          <t>R$ 200,00</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,3%</t>
+        <v>28</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 55,6%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1501,19 +1501,19 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
+          <t>R$ 239,00</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>▼ 44,4%</t>
+          <t>▼ 13,7%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>▼ 26,8%</t>
+          <t>▼ 30,8%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1574,19 +1574,19 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 259,00</t>
+          <t>R$ 277,00</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>▲ 29,5%</t>
+          <t>▲ 40,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>26</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,9%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1647,19 +1647,19 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 200,00</t>
+          <t>R$ 197,00</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>▼ 26,2%</t>
+          <t>▼ 57,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>44</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,7%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1720,19 +1720,19 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1757,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 271,00</t>
+          <t>R$ 467,00</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,5%</t>
+          <t>▲ 29,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 2,8%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1793,19 +1793,19 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 362,00</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>▲ 120,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>▲ 81,2%</t>
+        <v>36</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1866,19 +1866,19 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1903,33 +1903,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,1%</t>
+          <t>R$ 164,00</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>42</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 61,5%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1939,19 +1939,19 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 271,00</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>▲ 99,3%</t>
+          <t>R$ 132,00</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>▲ 23,1%</t>
+          <t>▲ 23,8%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2012,19 +2012,19 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
+          <t>R$ 197,00</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,0%</t>
+          <t>▼ 32,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 4,0%</t>
+        <v>21</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 32,3%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2085,19 +2085,19 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2122,33 +2122,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>▲ 49,3%</t>
+          <t>R$ 291,00</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 26,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>31</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 22,5%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2158,19 +2158,19 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,0%</t>
+          <t>R$ 395,00</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 42,9%</t>
+        <v>40</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 359,00</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 56,2%</t>
+        <v>56</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>▲ 30,2%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2341,33 +2341,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
+          <t>R$ 287,00</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>▲ 198,5%</t>
+          <t>▲ 99,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 46,7%</t>
+        <v>43</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,5%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 144,00</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 42,6%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▲ 37,9%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2487,33 +2487,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
+          <t>R$ 251,00</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 74,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 17,1%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2560,33 +2560,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
+          <t>R$ 144,00</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>▼ 72,7%</t>
+          <t>▼ 49,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,2%</t>
+        <v>35</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,4%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2633,33 +2633,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 373,00</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 92,3%</t>
+          <t>R$ 287,00</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,2%</t>
+          <t>▼ 31,9%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2706,33 +2706,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 194,00</t>
+          <t>R$ 503,00</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>▲ 385,0%</t>
+          <t>▲ 179,4%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,3%</t>
+        <v>47</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▲ 27,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2779,33 +2779,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
+          <t>R$ 180,00</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▼ 16,3%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>▲ 2,5%</t>
+          <t>▲ 37,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2852,33 +2852,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 200,00</t>
+          <t>R$ 215,00</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,6%</t>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,9%</t>
+        <v>27</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▲ 17,4%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2925,33 +2925,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 255,00</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 43,0%</t>
+          <t>R$ 287,00</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,2%</t>
+          <t>▼ 20,7%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 447,00</t>
+          <t>R$ 251,00</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>▲ 598,4%</t>
+          <t>▲ 74,3%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▲ 21,6%</t>
+        <v>29</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,3%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3071,33 +3071,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 64,00</t>
+          <t>R$ 144,00</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>▼ 81,8%</t>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,9%</t>
+          <t>▼ 26,8%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3144,33 +3144,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 351,00</t>
+          <t>R$ 259,00</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>▲ 82,8%</t>
+          <t>▲ 29,5%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>▲ 81,1%</t>
+        <v>41</v>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3217,33 +3217,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 200,00</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 26,2%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 9,8%</t>
+        <v>41</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3290,33 +3290,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 55,4%</t>
+          <t>R$ 271,00</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,5%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>▲ 24,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3363,33 +3363,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 287,00</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>▲ 49,5%</t>
+          <t>R$ 203,00</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 35,3%</t>
+        <v>29</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 81,2%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3436,25 +3436,25 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 203,00</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▲ 15,9%</t>
+        <v>16</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3509,33 +3509,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 59,9%</t>
+          <t>R$ 271,00</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,3%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,3%</t>
+        <v>32</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 23,1%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3582,33 +3582,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 479,00</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>▲ 15,4%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▲ 4,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3655,33 +3655,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 415,00</t>
+          <t>R$ 203,00</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>▲ 86,1%</t>
+          <t>▲ 49,3%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>25</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3728,33 +3728,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>▲ 39,4%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>20</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▲ 42,9%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3801,33 +3801,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 160,00</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+          <t>R$ 203,00</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>14</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 56,2%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3874,25 +3874,25 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
+          <t>R$ 203,00</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 198,5%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3947,33 +3947,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>▼ 42,6%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 36,8%</t>
+        <v>60</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4020,33 +4020,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,1%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>▲ 65,2%</t>
+        <v>24</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4093,33 +4093,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 319,00</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 121,5%</t>
+          <t>R$ 102,00</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 72,7%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>▼ 8,0%</t>
+          <t>▼ 15,2%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4166,33 +4166,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 46,9%</t>
+          <t>R$ 373,00</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>▲ 92,3%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>▲ 4,2%</t>
+        <v>33</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,2%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4239,33 +4239,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 271,00</t>
+          <t>R$ 194,00</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>▲ 697,1%</t>
+          <t>▲ 385,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>38</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,3%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4312,25 +4312,25 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,4%</t>
+        <v>41</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2,5%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4385,38 +4385,38 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
+          <t>R$ 200,00</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 21,6%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>▼ 8,0%</t>
+          <t>▼ 14,9%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4458,33 +4458,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,9%</t>
+          <t>R$ 255,00</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 43,0%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>▼ 3,8%</t>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4531,33 +4531,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,6%</t>
+          <t>R$ 447,00</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 598,4%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>▲ 8,3%</t>
+          <t>▲ 21,6%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4574,12 +4574,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4604,38 +4604,38 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
-        </is>
-      </c>
-      <c r="H57" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 64,00</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 81,8%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>▼ 41,5%</t>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4677,38 +4677,38 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 351,00</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 82,8%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>▲ 7,9%</t>
+          <t>▲ 81,1%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4750,33 +4750,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 192,00</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▲ 52,0%</t>
+        <v>37</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,8%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4793,12 +4793,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4823,33 +4823,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 128,00</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 55,4%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,8%</t>
+        <v>41</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,2%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4896,33 +4896,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 287,00</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,1%</t>
+          <t>▲ 49,5%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>▲ 7,4%</t>
+        <v>33</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 35,3%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4972,22 +4972,22 @@
           <t>R$ 192,00</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,9%</t>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,6%</t>
+        <v>51</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,9%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5012,12 +5012,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5042,33 +5042,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H63" s="4" t="inlineStr">
-        <is>
-          <t>▲ 6,2%</t>
+          <t>R$ 192,00</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 59,9%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>44</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,3%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5085,78 +5085,1611 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>R$ 479,00</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,4%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>29,2%</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>R$ 415,00</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>▲ 86,1%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>31,0%</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5,2%</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 39,4%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>R$ 160,00</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>R$ 192,00</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>R$ 128,00</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,6%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,8%</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,1%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 65,2%</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>18,4%</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>R$ 319,00</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>▲ 121,5%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,0%</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>43,5%</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,9%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 4,2%</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>16,0%</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>R$ 271,00</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>▲ 697,1%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,4%</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>6,3%</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>R$ 102,00</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,0%</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>13,0%</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,9%</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,8%</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>16,0%</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,6%</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,3%</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>11,5%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 128,00</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 41,5%</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 96,00</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,9%</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>7,3%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 96,00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 52,0%</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>7,9%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,8%</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,1%</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,4%</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>24,1%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 192,00</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,9%</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,6%</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,2%</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>UTD-014-BR</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>Apoio cocoras</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>5333038712</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>R$ 39,90</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>R$ 210,00</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="n">
+      <c r="I85" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="J64" s="2" t="inlineStr">
+      <c r="J85" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K64" s="2" t="inlineStr">
+      <c r="K85" s="2" t="inlineStr">
         <is>
           <t>33,3%</t>
         </is>
       </c>
-      <c r="L64" s="2" t="n">
+      <c r="L85" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="M64" s="2" t="inlineStr">
+      <c r="M85" s="2" t="inlineStr">
         <is>
           <t>2,3%</t>
         </is>
       </c>
-      <c r="N64" s="2" t="inlineStr">
-        <is>
-          <t>Básica</t>
-        </is>
-      </c>
-      <c r="O64" s="2" t="inlineStr">
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O64"/>
+  <autoFilter ref="A1:O85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-014-BR-APOIO-COCORAS.xlsx
+++ b/saida_skus/SKU_UTD-014-BR-APOIO-COCORAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$86</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -592,22 +592,22 @@
           <t>R$ 108,00</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,6%</t>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,1%</t>
+          <t>▼ 41,9%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
@@ -615,7 +615,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 323,00</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,2%</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,6%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>▲ 43,5%</t>
+        <v>31</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,1%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 215,00</t>
+          <t>R$ 323,00</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>▲ 198,6%</t>
+          <t>▲ 50,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 36,1%</t>
+        <v>33</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 43,5%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,5%</t>
+          <t>R$ 215,00</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 198,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>▲ 28,6%</t>
+        <v>23</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,1%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 215,00</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 19,4%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>36</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 180,00</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 32,6%</t>
+          <t>R$ 215,00</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>▲ 19,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,7%</t>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 267,00</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,9%</t>
+          <t>R$ 180,00</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 32,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 38,6%</t>
+        <v>28</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 160,00</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 55,4%</t>
+          <t>R$ 267,00</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,9%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>27</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 38,6%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1173,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 359,00</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,2%</t>
+          <t>R$ 160,00</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 55,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 2,2%</t>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 239,00</t>
+          <t>R$ 359,00</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>▲ 99,2%</t>
+          <t>▲ 50,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>▲ 45,2%</t>
+        <v>44</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,2%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 120,00</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,0%</t>
+          <t>R$ 239,00</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>45</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 45,2%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,14 +1362,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 279,00</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>▲ 39,5%</t>
+          <t>R$ 120,00</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>31</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 200,00</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,3%</t>
+          <t>R$ 279,00</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 39,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 55,6%</t>
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,14 +1508,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1538,29 +1538,29 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 239,00</t>
+          <t>R$ 200,00</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,7%</t>
+          <t>▼ 16,3%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,8%</t>
+        <v>28</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>▲ 55,6%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>▲ 40,6%</t>
+          <t>R$ 239,00</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,9%</t>
+          <t>▼ 30,8%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,14 +1654,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 197,00</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,8%</t>
+          <t>R$ 277,00</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,7%</t>
+        <v>26</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,9%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,14 +1727,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1757,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 467,00</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>▲ 29,0%</t>
+          <t>R$ 197,00</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 2,8%</t>
+        <v>44</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,7%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,14 +1800,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 362,00</t>
+          <t>R$ 467,00</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>▲ 120,7%</t>
+          <t>▲ 29,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 2,8%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,14 +1873,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1903,33 +1903,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 164,00</t>
+          <t>R$ 362,00</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>▲ 24,2%</t>
+          <t>▲ 120,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 61,5%</t>
+        <v>36</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,14 +1946,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 132,00</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,0%</t>
+          <t>R$ 164,00</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,2%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>▲ 23,8%</t>
+          <t>▲ 61,5%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,14 +2019,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 197,00</t>
+          <t>R$ 132,00</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>▼ 32,3%</t>
+          <t>▼ 33,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 32,3%</t>
+        <v>26</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 23,8%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,14 +2092,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2122,33 +2122,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 291,00</t>
+          <t>R$ 197,00</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>▼ 26,3%</t>
+          <t>▼ 32,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>▼ 22,5%</t>
+          <t>▼ 32,3%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,14 +2165,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,0%</t>
+          <t>R$ 291,00</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 26,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>▼ 28,6%</t>
+          <t>▼ 22,5%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2231,21 +2231,21 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 359,00</t>
+          <t>R$ 395,00</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,1%</t>
+          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▲ 30,2%</t>
+        <v>40</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,14 +2311,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2341,33 +2341,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 287,00</t>
+          <t>R$ 359,00</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>▲ 99,3%</t>
+          <t>▲ 25,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>▲ 7,5%</t>
+          <t>▲ 30,2%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,14 +2384,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,6%</t>
+          <t>R$ 287,00</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,3%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>▲ 37,9%</t>
+          <t>▲ 7,5%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,14 +2457,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2487,33 +2487,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 251,00</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 74,3%</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,6%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 17,1%</t>
+        <v>40</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,9%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,14 +2530,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2560,33 +2560,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,8%</t>
+          <t>R$ 251,00</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>▲ 74,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▲ 9,4%</t>
+        <v>29</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 17,1%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,14 +2603,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2633,33 +2633,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 287,00</t>
+          <t>R$ 144,00</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>▼ 42,9%</t>
+          <t>▼ 49,8%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 31,9%</t>
+        <v>35</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,4%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,14 +2676,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2706,33 +2706,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 503,00</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>▲ 179,4%</t>
+          <t>R$ 287,00</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>▲ 27,0%</t>
+        <v>32</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 31,9%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,14 +2749,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2779,33 +2779,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 180,00</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,3%</t>
+          <t>R$ 503,00</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 179,4%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>▲ 37,0%</t>
+          <t>▲ 27,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,14 +2822,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2852,33 +2852,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 215,00</t>
+          <t>R$ 180,00</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,1%</t>
+          <t>▼ 16,3%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>▲ 17,4%</t>
+          <t>▲ 37,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,14 +2895,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2925,33 +2925,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 287,00</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+          <t>R$ 215,00</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,7%</t>
+        <v>27</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 17,4%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,14 +2968,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 251,00</t>
+          <t>R$ 287,00</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>▲ 74,3%</t>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>▼ 3,3%</t>
+          <t>▼ 20,7%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,14 +3041,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3071,33 +3071,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+          <t>R$ 251,00</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 74,3%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>▼ 26,8%</t>
+          <t>▼ 3,3%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3114,14 +3114,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3144,33 +3144,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 259,00</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>▲ 29,5%</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>30</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 26,8%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,14 +3187,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3217,12 +3217,12 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 200,00</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 26,2%</t>
+          <t>R$ 259,00</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 29,5%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
@@ -3230,20 +3230,20 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,14 +3260,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3290,33 +3290,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 271,00</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,5%</t>
+          <t>R$ 200,00</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 26,2%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>41</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,14 +3333,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3363,33 +3363,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 271,00</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,5%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▲ 81,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3406,14 +3406,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3439,30 +3439,30 @@
           <t>R$ 203,00</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,1%</t>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>29</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▲ 81,2%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,14 +3479,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3509,33 +3509,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 271,00</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 99,3%</t>
+          <t>R$ 203,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 23,1%</t>
+        <v>16</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3552,14 +3552,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3582,33 +3582,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,0%</t>
+          <t>R$ 271,00</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,3%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>▲ 4,0%</t>
+          <t>▲ 23,1%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,14 +3625,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3655,33 +3655,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>▲ 49,3%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 4,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3698,14 +3698,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3728,33 +3728,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,0%</t>
+          <t>R$ 203,00</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>▲ 49,3%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>▲ 42,9%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,14 +3771,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3801,33 +3801,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 56,2%</t>
+        <v>20</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 42,9%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3844,14 +3844,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3877,22 +3877,22 @@
           <t>R$ 203,00</t>
         </is>
       </c>
-      <c r="H47" s="4" t="inlineStr">
-        <is>
-          <t>▲ 198,5%</t>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>▼ 46,7%</t>
+          <t>▼ 56,2%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,14 +3917,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3947,33 +3947,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 203,00</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>▲ 198,5%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>32</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3990,14 +3990,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4020,33 +4020,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H49" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>60</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4063,14 +4063,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4093,33 +4093,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 72,7%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,2%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4136,14 +4136,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4166,33 +4166,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 373,00</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>▲ 92,3%</t>
+          <t>R$ 102,00</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 72,7%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,2%</t>
+          <t>▼ 15,2%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4209,14 +4209,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4239,33 +4239,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 194,00</t>
+          <t>R$ 373,00</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>▲ 385,0%</t>
+          <t>▲ 92,3%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,3%</t>
+          <t>▼ 13,2%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4282,14 +4282,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4312,33 +4312,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+          <t>R$ 194,00</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>▲ 385,0%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2,5%</t>
+        <v>38</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,3%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
+          <t>13,2%</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
           <t>2,4%</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4355,14 +4355,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4385,33 +4385,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 200,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,6%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,9%</t>
+        <v>41</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2,5%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4428,14 +4428,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4458,33 +4458,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 255,00</t>
+          <t>R$ 200,00</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>▼ 43,0%</t>
+          <t>▼ 21,6%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,2%</t>
+          <t>▼ 14,9%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4501,14 +4501,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4531,33 +4531,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 447,00</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 598,4%</t>
+          <t>R$ 255,00</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 43,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 21,6%</t>
+        <v>47</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4574,14 +4574,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4604,33 +4604,33 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 64,00</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 81,8%</t>
+          <t>R$ 447,00</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>▲ 598,4%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,9%</t>
+        <v>62</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21,6%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4647,14 +4647,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4677,33 +4677,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 351,00</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 82,8%</t>
+          <t>R$ 64,00</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 81,8%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 81,1%</t>
+        <v>51</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4720,14 +4720,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4750,33 +4750,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
+          <t>R$ 351,00</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 82,8%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 9,8%</t>
+        <v>67</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>▲ 81,1%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4793,14 +4793,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4823,33 +4823,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 55,4%</t>
+          <t>R$ 192,00</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 24,2%</t>
+        <v>37</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,8%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4866,14 +4866,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4896,33 +4896,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 287,00</t>
-        </is>
-      </c>
-      <c r="H61" s="4" t="inlineStr">
-        <is>
-          <t>▲ 49,5%</t>
+          <t>R$ 128,00</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 55,4%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 35,3%</t>
+        <v>41</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,2%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4939,14 +4939,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4969,33 +4969,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 287,00</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 49,5%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 15,9%</t>
+        <v>33</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 35,3%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5012,14 +5012,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5045,22 +5045,22 @@
           <t>R$ 192,00</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 59,9%</t>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,3%</t>
+        <v>51</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,9%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5085,14 +5085,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5115,33 +5115,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 479,00</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 15,4%</t>
+          <t>R$ 192,00</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 59,9%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>44</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,3%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5158,14 +5158,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5188,33 +5188,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 415,00</t>
+          <t>R$ 479,00</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>▲ 86,1%</t>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>48</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5231,14 +5231,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5261,16 +5261,16 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 415,00</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>▲ 39,4%</t>
+          <t>▲ 86,1%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5279,15 +5279,15 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5304,14 +5304,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5334,12 +5334,12 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 160,00</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>▲ 39,4%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5377,14 +5377,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5407,20 +5407,20 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 160,00</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5429,11 +5429,11 @@
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5450,14 +5450,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5480,33 +5480,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,6%</t>
+          <t>R$ 192,00</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▼ 36,8%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5523,14 +5523,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5553,33 +5553,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 128,00</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>▼ 30,1%</t>
+          <t>▼ 42,6%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 65,2%</t>
+        <v>24</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,8%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5596,14 +5596,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5626,33 +5626,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 319,00</t>
-        </is>
-      </c>
-      <c r="H71" s="4" t="inlineStr">
-        <is>
-          <t>▲ 121,5%</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,1%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,0%</t>
+        <v>38</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▲ 65,2%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5669,14 +5669,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5699,33 +5699,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 46,9%</t>
+          <t>R$ 319,00</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 121,5%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 4,2%</t>
+        <v>23</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5742,14 +5742,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5772,33 +5772,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 271,00</t>
-        </is>
-      </c>
-      <c r="H73" s="4" t="inlineStr">
-        <is>
-          <t>▲ 697,1%</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,9%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 4,2%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5815,14 +5815,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5845,33 +5845,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 271,00</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 697,1%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,4%</t>
+        <v>24</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5888,14 +5888,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5918,38 +5918,38 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>▼ 8,0%</t>
+          <t>▼ 30,4%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
@@ -5961,14 +5961,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5991,38 +5991,38 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,9%</t>
+          <t>R$ 102,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▼ 3,8%</t>
+          <t>▼ 8,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
@@ -6034,14 +6034,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -6064,33 +6064,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,6%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,9%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>▲ 8,3%</t>
+        <v>25</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,8%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6107,14 +6107,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -6137,38 +6137,38 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 41,5%</t>
+        <v>26</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
@@ -6180,14 +6180,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -6210,33 +6210,33 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 128,00</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>▲ 7,9%</t>
+        <v>24</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 41,5%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6253,14 +6253,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -6288,20 +6288,20 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>▲ 52,0%</t>
+          <t>▲ 7,9%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
@@ -6309,12 +6309,12 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
@@ -6326,14 +6326,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -6356,33 +6356,33 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 96,00</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,8%</t>
+        <v>38</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▲ 52,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6399,14 +6399,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -6429,33 +6429,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 7,4%</t>
+        <v>25</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,8%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6472,14 +6472,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -6502,33 +6502,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,9%</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,1%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,6%</t>
+        <v>29</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,4%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6545,14 +6545,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -6575,33 +6575,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 6,2%</t>
+          <t>R$ 192,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,9%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>27</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,6%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6618,14 +6618,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -6648,25 +6648,25 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,2%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>28</v>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
@@ -6674,22 +6674,95 @@
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
           <t>2,3%</t>
         </is>
       </c>
-      <c r="N85" s="2" t="inlineStr">
-        <is>
-          <t>Básica</t>
-        </is>
-      </c>
-      <c r="O85" s="2" t="inlineStr">
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O85"/>
+  <autoFilter ref="A1:O86"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-014-BR-APOIO-COCORAS.xlsx
+++ b/saida_skus/SKU_UTD-014-BR-APOIO-COCORAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$87</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O86"/>
+  <dimension ref="A1:O87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 41,9%</t>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -665,22 +665,22 @@
           <t>R$ 108,00</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,6%</t>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,1%</t>
+          <t>▼ 41,9%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
@@ -688,7 +688,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 323,00</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,2%</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 43,5%</t>
+        <v>31</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,1%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 215,00</t>
+          <t>R$ 323,00</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>▲ 198,6%</t>
+          <t>▲ 50,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 36,1%</t>
+        <v>33</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 43,5%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,5%</t>
+          <t>R$ 215,00</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 198,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 28,6%</t>
+        <v>23</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,1%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 215,00</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>▲ 19,4%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>36</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 180,00</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 32,6%</t>
+          <t>R$ 215,00</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 19,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,7%</t>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 267,00</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,9%</t>
+          <t>R$ 180,00</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 32,6%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 38,6%</t>
+        <v>28</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,7%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1173,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 160,00</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 55,4%</t>
+          <t>R$ 267,00</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>27</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 38,6%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 359,00</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,2%</t>
+          <t>R$ 160,00</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 55,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 2,2%</t>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 239,00</t>
+          <t>R$ 359,00</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>▲ 99,2%</t>
+          <t>▲ 50,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 45,2%</t>
+        <v>44</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,2%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,14 +1362,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 120,00</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,0%</t>
+          <t>R$ 239,00</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>45</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▲ 45,2%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 279,00</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 39,5%</t>
+          <t>R$ 120,00</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>31</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,14 +1508,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 200,00</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,3%</t>
+          <t>R$ 279,00</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>▲ 39,5%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>▲ 55,6%</t>
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1611,29 +1611,29 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 239,00</t>
+          <t>R$ 200,00</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,7%</t>
+          <t>▼ 16,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,8%</t>
+        <v>28</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 55,6%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
@@ -1654,14 +1654,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>▲ 40,6%</t>
+          <t>R$ 239,00</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,9%</t>
+          <t>▼ 30,8%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,14 +1727,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1757,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 197,00</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,8%</t>
+          <t>R$ 277,00</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,7%</t>
+        <v>26</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,9%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,14 +1800,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 467,00</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>▲ 29,0%</t>
+          <t>R$ 197,00</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 2,8%</t>
+        <v>44</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,7%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,14 +1873,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1903,33 +1903,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 362,00</t>
+          <t>R$ 467,00</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>▲ 120,7%</t>
+          <t>▲ 29,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 2,8%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,14 +1946,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 164,00</t>
+          <t>R$ 362,00</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>▲ 24,2%</t>
+          <t>▲ 120,7%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▲ 61,5%</t>
+        <v>36</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,14 +2019,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 132,00</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,0%</t>
+          <t>R$ 164,00</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>▲ 23,8%</t>
+          <t>▲ 61,5%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,14 +2092,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2122,33 +2122,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 197,00</t>
+          <t>R$ 132,00</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>▼ 32,3%</t>
+          <t>▼ 33,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 32,3%</t>
+        <v>26</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 23,8%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,14 +2165,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 291,00</t>
+          <t>R$ 197,00</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>▼ 26,3%</t>
+          <t>▼ 32,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>▼ 22,5%</t>
+          <t>▼ 32,3%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,14 +2238,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,0%</t>
+          <t>R$ 291,00</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 26,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>▼ 28,6%</t>
+          <t>▼ 22,5%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2304,21 +2304,21 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2341,33 +2341,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 359,00</t>
+          <t>R$ 395,00</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,1%</t>
+          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 30,2%</t>
+        <v>40</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,14 +2384,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 287,00</t>
+          <t>R$ 359,00</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>▲ 99,3%</t>
+          <t>▲ 25,1%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>▲ 7,5%</t>
+          <t>▲ 30,2%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,14 +2457,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2487,33 +2487,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,6%</t>
+          <t>R$ 287,00</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>▲ 37,9%</t>
+          <t>▲ 7,5%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,14 +2530,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2560,33 +2560,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 251,00</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>▲ 74,3%</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 17,1%</t>
+        <v>40</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,9%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,14 +2603,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2633,33 +2633,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,8%</t>
+          <t>R$ 251,00</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 74,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 9,4%</t>
+        <v>29</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 17,1%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,14 +2676,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2706,33 +2706,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 287,00</t>
+          <t>R$ 144,00</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>▼ 42,9%</t>
+          <t>▼ 49,8%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 31,9%</t>
+        <v>35</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,4%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,14 +2749,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2779,33 +2779,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 503,00</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 179,4%</t>
+          <t>R$ 287,00</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 27,0%</t>
+        <v>32</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 31,9%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,14 +2822,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2852,33 +2852,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 180,00</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,3%</t>
+          <t>R$ 503,00</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>▲ 179,4%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>▲ 37,0%</t>
+          <t>▲ 27,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,14 +2895,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2925,33 +2925,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 215,00</t>
+          <t>R$ 180,00</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,1%</t>
+          <t>▼ 16,3%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>▲ 17,4%</t>
+          <t>▲ 37,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,14 +2968,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 287,00</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+          <t>R$ 215,00</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,7%</t>
+        <v>27</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▲ 17,4%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,14 +3041,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3071,33 +3071,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 251,00</t>
+          <t>R$ 287,00</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>▲ 74,3%</t>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>▼ 3,3%</t>
+          <t>▼ 20,7%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3114,14 +3114,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3144,33 +3144,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+          <t>R$ 251,00</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>▲ 74,3%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>▼ 26,8%</t>
+          <t>▼ 3,3%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,14 +3187,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3217,33 +3217,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 259,00</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 29,5%</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>30</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 26,8%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,14 +3260,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3290,12 +3290,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 200,00</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 26,2%</t>
+          <t>R$ 259,00</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>▲ 29,5%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
@@ -3303,20 +3303,20 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,14 +3333,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3363,33 +3363,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 271,00</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,5%</t>
+          <t>R$ 200,00</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 26,2%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>41</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3406,14 +3406,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3436,33 +3436,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 271,00</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,5%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▲ 81,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,14 +3479,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3512,30 +3512,30 @@
           <t>R$ 203,00</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,1%</t>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>29</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 81,2%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3552,14 +3552,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3582,33 +3582,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 271,00</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>▲ 99,3%</t>
+          <t>R$ 203,00</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>▲ 23,1%</t>
+        <v>16</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,14 +3625,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3655,33 +3655,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,0%</t>
+          <t>R$ 271,00</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,3%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>▲ 4,0%</t>
+          <t>▲ 23,1%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3698,14 +3698,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3728,33 +3728,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>▲ 49,3%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 4,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,14 +3771,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3801,33 +3801,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,0%</t>
+          <t>R$ 203,00</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 49,3%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>▲ 42,9%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3844,14 +3844,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3874,33 +3874,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,0%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 56,2%</t>
+        <v>20</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>▲ 42,9%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,14 +3917,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3950,22 +3950,22 @@
           <t>R$ 203,00</t>
         </is>
       </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>▲ 198,5%</t>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>▼ 46,7%</t>
+          <t>▼ 56,2%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3990,14 +3990,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4020,33 +4020,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 203,00</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>▲ 198,5%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>32</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4063,14 +4063,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4093,33 +4093,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>60</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4136,14 +4136,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4166,33 +4166,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 72,7%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,2%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4209,14 +4209,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4239,33 +4239,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 373,00</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>▲ 92,3%</t>
+          <t>R$ 102,00</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 72,7%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,2%</t>
+          <t>▼ 15,2%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4282,14 +4282,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4312,33 +4312,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 194,00</t>
+          <t>R$ 373,00</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>▲ 385,0%</t>
+          <t>▲ 92,3%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,3%</t>
+          <t>▼ 13,2%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4355,14 +4355,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4385,33 +4385,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+          <t>R$ 194,00</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 385,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2,5%</t>
+        <v>38</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,3%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
+          <t>13,2%</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
           <t>2,4%</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4428,14 +4428,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4458,33 +4458,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 200,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,6%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,9%</t>
+        <v>41</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2,5%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4501,14 +4501,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4531,33 +4531,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 255,00</t>
+          <t>R$ 200,00</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>▼ 43,0%</t>
+          <t>▼ 21,6%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,2%</t>
+          <t>▼ 14,9%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4574,14 +4574,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4604,33 +4604,33 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 447,00</t>
-        </is>
-      </c>
-      <c r="H57" s="4" t="inlineStr">
-        <is>
-          <t>▲ 598,4%</t>
+          <t>R$ 255,00</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 43,0%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>▲ 21,6%</t>
+        <v>47</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4647,14 +4647,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4677,33 +4677,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 64,00</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 81,8%</t>
+          <t>R$ 447,00</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 598,4%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,9%</t>
+        <v>62</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21,6%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4720,14 +4720,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4750,33 +4750,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 351,00</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>▲ 82,8%</t>
+          <t>R$ 64,00</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 81,8%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▲ 81,1%</t>
+        <v>51</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4793,14 +4793,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4823,33 +4823,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
+          <t>R$ 351,00</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 82,8%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 9,8%</t>
+        <v>67</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 81,1%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4866,14 +4866,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4896,33 +4896,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 55,4%</t>
+          <t>R$ 192,00</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>▲ 24,2%</t>
+        <v>37</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,8%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4939,14 +4939,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4969,33 +4969,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 287,00</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 49,5%</t>
+          <t>R$ 128,00</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 55,4%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 35,3%</t>
+        <v>41</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,2%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5012,14 +5012,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5042,33 +5042,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 287,00</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>▲ 49,5%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>▲ 15,9%</t>
+        <v>33</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 35,3%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5085,14 +5085,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5118,22 +5118,22 @@
           <t>R$ 192,00</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 59,9%</t>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,3%</t>
+        <v>51</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,9%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5158,14 +5158,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5188,33 +5188,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 479,00</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>▲ 15,4%</t>
+          <t>R$ 192,00</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 59,9%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>44</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,3%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5231,14 +5231,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5261,33 +5261,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 415,00</t>
+          <t>R$ 479,00</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>▲ 86,1%</t>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>48</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5304,14 +5304,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5334,16 +5334,16 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 415,00</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>▲ 39,4%</t>
+          <t>▲ 86,1%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5352,15 +5352,15 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5377,14 +5377,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5407,12 +5407,12 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 160,00</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 39,4%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5450,14 +5450,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5480,20 +5480,20 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
-        </is>
-      </c>
-      <c r="H69" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 160,00</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5502,11 +5502,11 @@
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5523,14 +5523,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5553,33 +5553,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,6%</t>
+          <t>R$ 192,00</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▼ 36,8%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5596,14 +5596,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5626,33 +5626,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 128,00</t>
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>▼ 30,1%</t>
+          <t>▼ 42,6%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▲ 65,2%</t>
+        <v>24</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,8%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5669,14 +5669,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5699,33 +5699,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 319,00</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 121,5%</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,1%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,0%</t>
+        <v>38</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 65,2%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5742,14 +5742,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5772,33 +5772,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 46,9%</t>
+          <t>R$ 319,00</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>▲ 121,5%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▲ 4,2%</t>
+        <v>23</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5815,14 +5815,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5845,33 +5845,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 271,00</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 697,1%</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,9%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 4,2%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5888,14 +5888,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5918,33 +5918,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 271,00</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>▲ 697,1%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,4%</t>
+        <v>24</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5961,14 +5961,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5991,38 +5991,38 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▼ 8,0%</t>
+          <t>▼ 30,4%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
@@ -6034,14 +6034,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -6064,38 +6064,38 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H77" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,9%</t>
+          <t>R$ 102,00</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>▼ 3,8%</t>
+          <t>▼ 8,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
@@ -6107,14 +6107,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -6137,33 +6137,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,6%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,9%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 8,3%</t>
+        <v>25</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,8%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6180,14 +6180,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -6210,38 +6210,38 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 41,5%</t>
+        <v>26</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -6253,14 +6253,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -6283,33 +6283,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 128,00</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 7,9%</t>
+        <v>24</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 41,5%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6326,14 +6326,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -6361,20 +6361,20 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>▲ 52,0%</t>
+          <t>▲ 7,9%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
@@ -6399,14 +6399,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -6429,33 +6429,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 96,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,8%</t>
+        <v>38</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 52,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6472,14 +6472,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -6502,33 +6502,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H83" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>▲ 7,4%</t>
+        <v>25</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,8%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6545,14 +6545,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -6575,33 +6575,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,9%</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,1%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,6%</t>
+        <v>29</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,4%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6618,14 +6618,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -6648,33 +6648,33 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H85" s="4" t="inlineStr">
-        <is>
-          <t>▲ 6,2%</t>
+          <t>R$ 192,00</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,9%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>27</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,6%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6691,14 +6691,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -6721,25 +6721,25 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,2%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>28</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
@@ -6747,22 +6747,95 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
           <t>2,3%</t>
         </is>
       </c>
-      <c r="N86" s="2" t="inlineStr">
-        <is>
-          <t>Básica</t>
-        </is>
-      </c>
-      <c r="O86" s="2" t="inlineStr">
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O86"/>
+  <autoFilter ref="A1:O87"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-014-BR-APOIO-COCORAS.xlsx
+++ b/saida_skus/SKU_UTD-014-BR-APOIO-COCORAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O87"/>
+  <dimension ref="A1:O88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 215,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 497,2%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 5,6%</t>
+          <t>▲ 35,3%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 41,9%</t>
+        <v>17</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -738,22 +738,22 @@
           <t>R$ 108,00</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,6%</t>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,1%</t>
+        <v>18</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 41,9%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
@@ -761,7 +761,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 323,00</t>
+          <t>R$ 108,00</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,2%</t>
+          <t>▼ 66,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>▲ 43,5%</t>
+          <t>▼ 6,1%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 215,00</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 198,6%</t>
+          <t>R$ 323,00</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>▼ 36,1%</t>
+          <t>▲ 43,5%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
+          <t>R$ 215,00</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,5%</t>
+          <t>▲ 198,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>▲ 28,6%</t>
+          <t>▼ 36,1%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 215,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>▲ 19,4%</t>
+          <t>▼ 66,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>36</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 180,00</t>
+          <t>R$ 215,00</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>▼ 32,6%</t>
+          <t>▲ 19,4%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,7%</t>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1173,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 267,00</t>
+          <t>R$ 180,00</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,9%</t>
+          <t>▼ 32,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 38,6%</t>
+          <t>▲ 3,7%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 160,00</t>
+          <t>R$ 267,00</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>▼ 55,4%</t>
+          <t>▲ 66,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>27</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>▼ 38,6%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 359,00</t>
+          <t>R$ 160,00</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,2%</t>
+          <t>▼ 55,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 2,2%</t>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,14 +1362,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 239,00</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>▲ 99,2%</t>
+          <t>R$ 359,00</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>▲ 45,2%</t>
+          <t>▼ 2,2%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 120,00</t>
+          <t>R$ 239,00</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>▼ 57,0%</t>
+          <t>▲ 99,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>45</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▲ 45,2%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,14 +1508,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 279,00</t>
+          <t>R$ 120,00</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>▲ 39,5%</t>
+          <t>▼ 57,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>31</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 200,00</t>
+          <t>R$ 279,00</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,3%</t>
+          <t>▲ 39,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>▲ 55,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,14 +1654,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1684,29 +1684,29 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 239,00</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,7%</t>
+          <t>R$ 200,00</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>▼ 30,8%</t>
+          <t>▲ 55,6%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
@@ -1727,14 +1727,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1757,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
+          <t>R$ 239,00</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>▲ 40,6%</t>
+          <t>▼ 13,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,9%</t>
+        <v>18</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▼ 30,8%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,14 +1800,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 197,00</t>
+          <t>R$ 277,00</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>▼ 57,8%</t>
+          <t>▲ 40,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,7%</t>
+          <t>▼ 40,9%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,14 +1873,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1903,33 +1903,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 467,00</t>
+          <t>R$ 197,00</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>▲ 29,0%</t>
+          <t>▼ 57,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>▼ 2,8%</t>
+          <t>▲ 25,7%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,14 +1946,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 362,00</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>▲ 120,7%</t>
+          <t>R$ 467,00</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>▲ 29,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>35</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>▼ 2,8%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,14 +2019,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 164,00</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 24,2%</t>
+          <t>R$ 362,00</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>▲ 120,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>▲ 61,5%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,14 +2092,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2122,33 +2122,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 132,00</t>
+          <t>R$ 164,00</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,0%</t>
+          <t>▲ 24,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>▲ 23,8%</t>
+        <v>42</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▲ 61,5%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,14 +2165,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 197,00</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 32,3%</t>
+          <t>R$ 132,00</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>▼ 32,3%</t>
+          <t>▲ 23,8%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,14 +2238,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 291,00</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 26,3%</t>
+          <t>R$ 197,00</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>▼ 32,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,5%</t>
+        <v>21</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>▼ 32,3%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,14 +2311,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2341,33 +2341,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
+          <t>R$ 291,00</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>▲ 10,0%</t>
+          <t>▼ 26,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+        <v>31</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▼ 22,5%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2377,21 +2377,21 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 359,00</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,1%</t>
+          <t>R$ 395,00</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>▲ 30,2%</t>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,14 +2457,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2487,33 +2487,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 287,00</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 99,3%</t>
+          <t>R$ 359,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,1%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 7,5%</t>
+        <v>56</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▲ 30,2%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,14 +2530,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2560,33 +2560,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
+          <t>R$ 287,00</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>▼ 42,6%</t>
+          <t>▲ 99,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▲ 37,9%</t>
+        <v>43</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▲ 7,5%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,14 +2603,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2633,33 +2633,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 251,00</t>
+          <t>R$ 144,00</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>▲ 74,3%</t>
+          <t>▼ 42,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>▼ 17,1%</t>
+          <t>▲ 37,9%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,14 +2676,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2706,33 +2706,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
+          <t>R$ 251,00</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>▼ 49,8%</t>
+          <t>▲ 74,3%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>▲ 9,4%</t>
+          <t>▼ 17,1%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,14 +2749,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2779,33 +2779,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 287,00</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>▼ 49,8%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>▼ 31,9%</t>
+          <t>▲ 9,4%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,14 +2822,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2852,33 +2852,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 503,00</t>
+          <t>R$ 287,00</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>▲ 179,4%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>▲ 27,0%</t>
+          <t>▼ 31,9%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,14 +2895,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2925,33 +2925,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 180,00</t>
+          <t>R$ 503,00</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,3%</t>
+          <t>▲ 179,4%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 37,0%</t>
+        <v>47</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▲ 27,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,14 +2968,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 215,00</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,1%</t>
+          <t>R$ 180,00</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,3%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▲ 17,4%</t>
+        <v>37</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▲ 37,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,14 +3041,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3071,33 +3071,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 287,00</t>
+          <t>R$ 215,00</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,7%</t>
+          <t>▲ 17,4%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3114,14 +3114,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3144,33 +3144,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 251,00</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>▲ 74,3%</t>
+          <t>R$ 287,00</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,3%</t>
+        <v>23</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>▼ 20,7%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,14 +3187,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3217,33 +3217,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
+          <t>R$ 251,00</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>▼ 44,4%</t>
+          <t>▲ 74,3%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 26,8%</t>
+        <v>29</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▼ 3,3%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,14 +3260,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3290,33 +3290,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 259,00</t>
+          <t>R$ 144,00</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>▲ 29,5%</t>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>30</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▼ 26,8%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,14 +3333,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3363,12 +3363,12 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 200,00</t>
+          <t>R$ 259,00</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>▼ 26,2%</t>
+          <t>▲ 29,5%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
@@ -3376,20 +3376,20 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3406,14 +3406,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3436,33 +3436,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 271,00</t>
+          <t>R$ 200,00</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,5%</t>
+          <t>▼ 26,2%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>41</v>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,14 +3479,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3509,33 +3509,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 271,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,5%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>▲ 81,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3552,14 +3552,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3585,30 +3585,30 @@
           <t>R$ 203,00</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,1%</t>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 81,2%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,14 +3625,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3655,33 +3655,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 271,00</t>
+          <t>R$ 203,00</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>▲ 99,3%</t>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>▲ 23,1%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3698,14 +3698,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3728,33 +3728,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
+          <t>R$ 271,00</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,0%</t>
+          <t>▲ 99,3%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>▲ 4,0%</t>
+        <v>32</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▲ 23,1%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,14 +3771,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3801,33 +3801,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>▲ 49,3%</t>
+          <t>▼ 33,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>26</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▲ 4,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3844,14 +3844,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3874,33 +3874,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
+          <t>R$ 203,00</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,0%</t>
+          <t>▲ 49,3%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>▲ 42,9%</t>
+        <v>25</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,14 +3917,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -3947,33 +3947,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>▼ 56,2%</t>
+          <t>▲ 42,9%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3990,14 +3990,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4023,22 +4023,22 @@
           <t>R$ 203,00</t>
         </is>
       </c>
-      <c r="H49" s="4" t="inlineStr">
-        <is>
-          <t>▲ 198,5%</t>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 46,7%</t>
+        <v>14</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>▼ 56,2%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4063,14 +4063,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4093,33 +4093,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 203,00</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 198,5%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4136,14 +4136,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4166,33 +4166,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4209,14 +4209,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4239,33 +4239,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>▼ 72,7%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,2%</t>
+        <v>24</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4282,14 +4282,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4312,33 +4312,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 373,00</t>
+          <t>R$ 102,00</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>▲ 92,3%</t>
+          <t>▼ 72,7%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,2%</t>
+        <v>28</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>▼ 15,2%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4355,14 +4355,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4385,33 +4385,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 194,00</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 385,0%</t>
+          <t>R$ 373,00</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▲ 92,3%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,3%</t>
+        <v>33</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▼ 13,2%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4428,14 +4428,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4458,33 +4458,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
+          <t>R$ 194,00</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▲ 385,0%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>▲ 2,5%</t>
+          <t>▼ 7,3%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
+          <t>13,2%</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
           <t>2,4%</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4501,14 +4501,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4531,33 +4531,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 200,00</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,6%</t>
+          <t>R$ 40,00</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,9%</t>
+          <t>▲ 2,5%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4574,14 +4574,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4604,33 +4604,33 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 255,00</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 43,0%</t>
+          <t>R$ 200,00</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>▼ 21,6%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,2%</t>
+        <v>40</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,9%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4647,14 +4647,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4677,33 +4677,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 447,00</t>
+          <t>R$ 255,00</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>▲ 598,4%</t>
+          <t>▼ 43,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>▲ 21,6%</t>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4720,14 +4720,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4750,33 +4750,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 64,00</t>
+          <t>R$ 447,00</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>▼ 81,8%</t>
+          <t>▲ 598,4%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,9%</t>
+          <t>▲ 21,6%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4793,14 +4793,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4823,33 +4823,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 351,00</t>
+          <t>R$ 64,00</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>▲ 82,8%</t>
+          <t>▼ 81,8%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>▲ 81,1%</t>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4866,14 +4866,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4896,33 +4896,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
-        </is>
-      </c>
-      <c r="H61" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 351,00</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>▲ 82,8%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>▼ 9,8%</t>
+          <t>▲ 81,1%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4939,14 +4939,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -4969,33 +4969,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
+          <t>R$ 192,00</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>▼ 55,4%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>▲ 24,2%</t>
+          <t>▼ 9,8%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5012,14 +5012,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5042,33 +5042,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 287,00</t>
+          <t>R$ 128,00</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>▲ 49,5%</t>
+          <t>▼ 55,4%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>▼ 35,3%</t>
+          <t>▲ 24,2%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5085,14 +5085,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5115,33 +5115,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 287,00</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▲ 49,5%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>▲ 15,9%</t>
+          <t>▼ 35,3%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5158,14 +5158,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5191,22 +5191,22 @@
           <t>R$ 192,00</t>
         </is>
       </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 59,9%</t>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>▼ 8,3%</t>
+          <t>▲ 15,9%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5231,14 +5231,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5261,33 +5261,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 479,00</t>
+          <t>R$ 192,00</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>▲ 15,4%</t>
+          <t>▼ 59,9%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▼ 8,3%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5304,14 +5304,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5334,33 +5334,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 415,00</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>▲ 86,1%</t>
+          <t>R$ 479,00</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>48</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5377,14 +5377,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5407,16 +5407,16 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 39,4%</t>
+          <t>R$ 415,00</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▲ 86,1%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5425,15 +5425,15 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5450,14 +5450,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5480,12 +5480,12 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 160,00</t>
+          <t>R$ 223,00</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▲ 39,4%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5523,14 +5523,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5553,20 +5553,20 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
+          <t>R$ 160,00</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5575,11 +5575,11 @@
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5596,14 +5596,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5626,33 +5626,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
+          <t>R$ 192,00</t>
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>▼ 42,6%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 36,8%</t>
+        <v>0</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5669,14 +5669,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5699,33 +5699,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,1%</t>
+          <t>R$ 128,00</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>▼ 42,6%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>▲ 65,2%</t>
+          <t>▼ 36,8%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5742,14 +5742,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5772,33 +5772,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 319,00</t>
+          <t>R$ 223,00</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>▲ 121,5%</t>
+          <t>▼ 30,1%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>▼ 8,0%</t>
+          <t>▲ 65,2%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5815,14 +5815,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5845,33 +5845,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
+          <t>R$ 319,00</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>▼ 46,9%</t>
+          <t>▲ 121,5%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>▲ 4,2%</t>
+          <t>▼ 8,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5888,14 +5888,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5918,33 +5918,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 271,00</t>
+          <t>R$ 144,00</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>▲ 697,1%</t>
+          <t>▼ 46,9%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>25</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▲ 4,2%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5961,14 +5961,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -5991,33 +5991,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 271,00</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 697,1%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▼ 30,4%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6034,14 +6034,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -6064,38 +6064,38 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,0%</t>
+        <v>16</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▼ 30,4%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
@@ -6107,14 +6107,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -6137,38 +6137,38 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
+          <t>R$ 102,00</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,9%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,8%</t>
+        <v>23</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▼ 8,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
@@ -6180,14 +6180,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -6210,33 +6210,33 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,6%</t>
+          <t>▲ 25,9%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>▲ 8,3%</t>
+          <t>▼ 3,8%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6253,14 +6253,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -6283,38 +6283,38 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
+          <t>R$ 108,00</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>▼ 41,5%</t>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
@@ -6326,14 +6326,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -6356,33 +6356,33 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 128,00</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>▲ 7,9%</t>
+          <t>▼ 41,5%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6399,14 +6399,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -6434,20 +6434,20 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 52,0%</t>
+        <v>41</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▲ 7,9%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
@@ -6472,14 +6472,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -6502,33 +6502,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 96,00</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,8%</t>
+          <t>▲ 52,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6545,14 +6545,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -6575,33 +6575,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>▲ 7,4%</t>
+          <t>▼ 13,8%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6618,14 +6618,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -6648,33 +6648,33 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
+          <t>R$ 223,00</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,9%</t>
+          <t>▲ 16,1%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>▼ 3,6%</t>
+          <t>▲ 7,4%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6691,14 +6691,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -6721,33 +6721,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 192,00</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>▲ 6,2%</t>
+          <t>▼ 13,9%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 3,6%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6764,14 +6764,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-014-BR</t>
@@ -6794,25 +6794,25 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>▲ 6,2%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>28</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
@@ -6820,22 +6820,95 @@
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
           <t>2,3%</t>
         </is>
       </c>
-      <c r="N87" s="2" t="inlineStr">
-        <is>
-          <t>Básica</t>
-        </is>
-      </c>
-      <c r="O87" s="2" t="inlineStr">
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O87"/>
+  <autoFilter ref="A1:O88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-014-BR-APOIO-COCORAS.xlsx
+++ b/saida_skus/SKU_UTD-014-BR-APOIO-COCORAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$92</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O88"/>
+  <dimension ref="A1:O92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 215,00</t>
+          <t>R$ 152,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▲ 497,2%</t>
+          <t>▲ 40,7%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▲ 35,3%</t>
+        <v>24</v>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>▼ 22,6%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 108,00</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>▼ 5,6%</t>
+          <t>▼ 13,9%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 180,00</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 41,9%</t>
+        <v>36</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
+          <t>R$ 144,00</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,6%</t>
+          <t>▼ 33,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>▼ 6,1%</t>
+        <v>34</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▲ 47,8%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 323,00</t>
+          <t>R$ 215,00</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,2%</t>
+          <t>▲ 497,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>▲ 43,5%</t>
+          <t>▲ 35,3%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 215,00</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>▲ 198,6%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>▼ 36,1%</t>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,5%</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▲ 28,6%</t>
+        <v>18</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▼ 41,9%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 215,00</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>▲ 19,4%</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,6%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>31</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>▼ 6,1%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 180,00</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>▼ 32,6%</t>
+          <t>R$ 323,00</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▲ 3,7%</t>
+          <t>▲ 43,5%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 267,00</t>
+          <t>R$ 215,00</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>▲ 66,9%</t>
+          <t>▲ 198,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>▼ 38,6%</t>
+          <t>▼ 36,1%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 160,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>▼ 55,4%</t>
+          <t>▼ 66,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>36</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 359,00</t>
+          <t>R$ 215,00</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,2%</t>
+          <t>▲ 19,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▼ 2,2%</t>
+        <v>28</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 239,00</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>▲ 99,2%</t>
+          <t>R$ 180,00</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>▼ 32,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>▲ 45,2%</t>
+          <t>▲ 3,7%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 120,00</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>▼ 57,0%</t>
+          <t>R$ 267,00</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>▲ 66,9%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>27</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>▼ 38,6%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 279,00</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>▲ 39,5%</t>
+          <t>R$ 160,00</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>▼ 55,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>44</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 200,00</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,3%</t>
+          <t>R$ 359,00</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▲ 55,6%</t>
+        <v>44</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▼ 2,2%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1760,22 +1760,22 @@
           <t>R$ 239,00</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>▼ 13,7%</t>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▲ 99,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▼ 30,8%</t>
+        <v>45</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▲ 45,2%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>▲ 40,6%</t>
+          <t>R$ 120,00</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>▼ 57,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>▼ 40,9%</t>
+        <v>31</v>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1903,33 +1903,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 197,00</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>▼ 57,8%</t>
+          <t>R$ 279,00</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▲ 39,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▲ 25,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 467,00</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>▲ 29,0%</t>
+          <t>R$ 200,00</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,3%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▼ 2,8%</t>
+        <v>28</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▲ 55,6%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 362,00</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>▲ 120,7%</t>
+          <t>R$ 239,00</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>▼ 13,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 30,8%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2122,33 +2122,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 164,00</t>
+          <t>R$ 277,00</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>▲ 24,2%</t>
+          <t>▲ 40,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▲ 61,5%</t>
+        <v>26</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▼ 40,9%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 132,00</t>
+          <t>R$ 197,00</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,0%</t>
+          <t>▼ 57,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>▲ 23,8%</t>
+          <t>▲ 25,7%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 197,00</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>▼ 32,3%</t>
+          <t>R$ 467,00</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>▲ 29,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>▼ 32,3%</t>
+          <t>▼ 2,8%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2341,33 +2341,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 291,00</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>▼ 26,3%</t>
+          <t>R$ 362,00</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>▲ 120,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>▼ 22,5%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
+          <t>R$ 164,00</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>▲ 10,0%</t>
+          <t>▲ 24,2%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+        <v>42</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▲ 61,5%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2450,19 +2450,19 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2487,33 +2487,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 359,00</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▲ 25,1%</t>
+          <t>R$ 132,00</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>▲ 30,2%</t>
+          <t>▲ 23,8%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2523,19 +2523,19 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2560,33 +2560,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 287,00</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>▲ 99,3%</t>
+          <t>R$ 197,00</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>▼ 32,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▲ 7,5%</t>
+        <v>21</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▼ 32,3%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2596,19 +2596,19 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2633,33 +2633,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
+          <t>R$ 291,00</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>▼ 42,6%</t>
+          <t>▼ 26,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▲ 37,9%</t>
+        <v>31</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▼ 22,5%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2669,19 +2669,19 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2706,33 +2706,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 251,00</t>
+          <t>R$ 395,00</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>▲ 74,3%</t>
+          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>▼ 17,1%</t>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2779,33 +2779,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>▼ 49,8%</t>
+          <t>R$ 359,00</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,1%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>▲ 9,4%</t>
+          <t>▲ 30,2%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2855,22 +2855,22 @@
           <t>R$ 287,00</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>▲ 99,3%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▼ 31,9%</t>
+        <v>43</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▲ 7,5%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2925,33 +2925,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 503,00</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▲ 179,4%</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>▼ 42,6%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▲ 27,0%</t>
+          <t>▲ 37,9%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 180,00</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,3%</t>
+          <t>R$ 251,00</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>▲ 74,3%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▲ 37,0%</t>
+        <v>29</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▼ 17,1%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3071,33 +3071,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 215,00</t>
+          <t>R$ 144,00</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,1%</t>
+          <t>▼ 49,8%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>▲ 17,4%</t>
+          <t>▲ 9,4%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3147,22 +3147,22 @@
           <t>R$ 287,00</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>▼ 20,7%</t>
+          <t>▼ 31,9%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3217,33 +3217,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 251,00</t>
+          <t>R$ 503,00</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>▲ 74,3%</t>
+          <t>▲ 179,4%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▼ 3,3%</t>
+        <v>47</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▲ 27,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3290,33 +3290,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
+          <t>R$ 180,00</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>▼ 44,4%</t>
+          <t>▼ 16,3%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>▼ 26,8%</t>
+        <v>37</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▲ 37,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3363,33 +3363,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 259,00</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▲ 29,5%</t>
+          <t>R$ 215,00</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>27</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▲ 17,4%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3436,33 +3436,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 200,00</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>▼ 26,2%</t>
+          <t>R$ 287,00</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>23</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▼ 20,7%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3509,33 +3509,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 271,00</t>
+          <t>R$ 251,00</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,5%</t>
+          <t>▲ 74,3%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 3,3%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3582,33 +3582,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▲ 81,2%</t>
+        <v>30</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>▼ 26,8%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3655,33 +3655,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,1%</t>
+          <t>R$ 259,00</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>▲ 29,5%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>41</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3728,33 +3728,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 271,00</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>▲ 99,3%</t>
+          <t>R$ 200,00</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>▼ 26,2%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▲ 23,1%</t>
+        <v>41</v>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3801,33 +3801,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,0%</t>
+          <t>R$ 271,00</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,5%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▲ 4,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3877,30 +3877,30 @@
           <t>R$ 203,00</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>▲ 49,3%</t>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 81,2%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3947,33 +3947,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
+          <t>R$ 203,00</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,0%</t>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▲ 42,9%</t>
+        <v>16</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4020,33 +4020,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 271,00</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>▲ 99,3%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>▼ 56,2%</t>
+        <v>32</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▲ 23,1%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4093,33 +4093,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>▲ 198,5%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▼ 46,7%</t>
+        <v>26</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▲ 4,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4166,33 +4166,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 203,00</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>▲ 49,3%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4242,22 +4242,22 @@
           <t>R$ 136,00</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>20</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▲ 42,9%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4312,33 +4312,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H53" s="4" t="inlineStr">
-        <is>
-          <t>▼ 72,7%</t>
+          <t>R$ 203,00</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>▼ 15,2%</t>
+          <t>▼ 56,2%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4385,33 +4385,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 373,00</t>
+          <t>R$ 203,00</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>▲ 92,3%</t>
+          <t>▲ 198,5%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>▼ 13,2%</t>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4458,33 +4458,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 194,00</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>▲ 385,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>▼ 7,3%</t>
+        <v>60</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4531,33 +4531,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▲ 2,5%</t>
+        <v>24</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4574,12 +4574,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4604,33 +4604,33 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 200,00</t>
+          <t>R$ 102,00</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>▼ 21,6%</t>
+          <t>▼ 72,7%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>▼ 14,9%</t>
+          <t>▼ 15,2%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4677,33 +4677,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 255,00</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>▼ 43,0%</t>
+          <t>R$ 373,00</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>▲ 92,3%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>▼ 24,2%</t>
+          <t>▼ 13,2%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4750,33 +4750,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 447,00</t>
+          <t>R$ 194,00</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>▲ 598,4%</t>
+          <t>▲ 385,0%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▲ 21,6%</t>
+        <v>38</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,3%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4793,12 +4793,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4823,29 +4823,29 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 64,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>▼ 81,8%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▼ 23,9%</t>
+        <v>41</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▲ 2,5%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -4866,12 +4866,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4896,33 +4896,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 351,00</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>▲ 82,8%</t>
+          <t>R$ 200,00</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>▼ 21,6%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▲ 81,1%</t>
+        <v>40</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,9%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4969,33 +4969,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 255,00</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>▼ 43,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>▼ 9,8%</t>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5012,12 +5012,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5042,33 +5042,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
-        </is>
-      </c>
-      <c r="H63" s="4" t="inlineStr">
-        <is>
-          <t>▼ 55,4%</t>
+          <t>R$ 447,00</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>▲ 598,4%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>▲ 24,2%</t>
+          <t>▲ 21,6%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5115,33 +5115,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 287,00</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▲ 49,5%</t>
+          <t>R$ 64,00</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>▼ 81,8%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>▼ 35,3%</t>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5188,33 +5188,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 351,00</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>▲ 82,8%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>▲ 15,9%</t>
+          <t>▲ 81,1%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5264,22 +5264,22 @@
           <t>R$ 192,00</t>
         </is>
       </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>▼ 59,9%</t>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>▼ 8,3%</t>
+          <t>▼ 9,8%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5304,12 +5304,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5334,33 +5334,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 479,00</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>▲ 15,4%</t>
+          <t>R$ 128,00</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>▼ 55,4%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▲ 24,2%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5377,12 +5377,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5407,33 +5407,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 415,00</t>
+          <t>R$ 287,00</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>▲ 86,1%</t>
+          <t>▲ 49,5%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>33</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▼ 35,3%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5450,12 +5450,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5480,29 +5480,29 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>▲ 39,4%</t>
+          <t>R$ 192,00</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>51</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▲ 15,9%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
@@ -5523,12 +5523,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5553,33 +5553,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 160,00</t>
+          <t>R$ 192,00</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 59,9%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>44</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▼ 8,3%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5626,33 +5626,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
+          <t>R$ 479,00</t>
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>48</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5699,33 +5699,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>▼ 42,6%</t>
+          <t>R$ 415,00</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>▲ 86,1%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▼ 36,8%</t>
+        <v>42</v>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5742,12 +5742,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5775,30 +5775,30 @@
           <t>R$ 223,00</t>
         </is>
       </c>
-      <c r="H73" s="4" t="inlineStr">
-        <is>
-          <t>▼ 30,1%</t>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>▲ 39,4%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▲ 65,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5845,33 +5845,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 319,00</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▲ 121,5%</t>
+          <t>R$ 160,00</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▼ 8,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5918,33 +5918,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H75" s="4" t="inlineStr">
-        <is>
-          <t>▼ 46,9%</t>
+          <t>R$ 192,00</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▲ 4,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5961,12 +5961,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5991,33 +5991,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 271,00</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▲ 697,1%</t>
+          <t>R$ 128,00</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>▼ 42,6%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▼ 36,8%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6064,33 +6064,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 223,00</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 30,1%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>▼ 30,4%</t>
+        <v>38</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▲ 65,2%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6107,12 +6107,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6137,12 +6137,12 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+          <t>R$ 319,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▲ 121,5%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
@@ -6155,20 +6155,20 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6210,20 +6210,20 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>▲ 25,9%</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>▼ 46,9%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>▼ 3,8%</t>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▲ 4,2%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6253,12 +6253,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6283,33 +6283,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>▼ 15,6%</t>
+          <t>R$ 271,00</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▲ 697,1%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>▲ 8,3%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6356,38 +6356,38 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 128,00</t>
-        </is>
-      </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>▼ 41,5%</t>
+          <t>▼ 30,4%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6429,25 +6429,25 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 102,00</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▲ 7,9%</t>
+        <v>23</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▼ 8,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
@@ -6455,7 +6455,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6502,33 +6502,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,9%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▲ 52,0%</t>
+        <v>25</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>▼ 3,8%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6545,12 +6545,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6575,33 +6575,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 108,00</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▼ 13,8%</t>
+        <v>26</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6648,38 +6648,38 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 128,00</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>▲ 16,1%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▲ 7,4%</t>
+        <v>24</v>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>▼ 41,5%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6721,38 +6721,38 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 192,00</t>
-        </is>
-      </c>
-      <c r="H86" s="4" t="inlineStr">
-        <is>
-          <t>▼ 13,9%</t>
+          <t>R$ 96,00</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▼ 3,6%</t>
+        <v>41</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▲ 7,9%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
@@ -6764,12 +6764,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6794,33 +6794,33 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H87" s="3" t="inlineStr">
-        <is>
-          <t>▲ 6,2%</t>
+          <t>R$ 96,00</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 52,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6837,78 +6837,370 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▼ 13,8%</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>▲ 16,1%</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▲ 7,4%</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>24,1%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 192,00</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>▼ 13,9%</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▼ 3,6%</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>▲ 6,2%</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>UTD-014-BR</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>Apoio cocoras</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>5333038712</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>R$ 39,90</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>UTD-014-BR</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Apoio cocoras</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>5333038712</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>R$ 210,00</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I88" s="2" t="n">
+      <c r="I92" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="J88" s="2" t="inlineStr">
+      <c r="J92" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K88" s="2" t="inlineStr">
+      <c r="K92" s="2" t="inlineStr">
         <is>
           <t>33,3%</t>
         </is>
       </c>
-      <c r="L88" s="2" t="n">
+      <c r="L92" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="M88" s="2" t="inlineStr">
+      <c r="M92" s="2" t="inlineStr">
         <is>
           <t>2,3%</t>
         </is>
       </c>
-      <c r="N88" s="2" t="inlineStr">
-        <is>
-          <t>Básica</t>
-        </is>
-      </c>
-      <c r="O88" s="2" t="inlineStr">
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O88"/>
+  <autoFilter ref="A1:O92"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>